--- a/Fondamentaux Grasshopper - IndC - 01-09-2026.xlsx
+++ b/Fondamentaux Grasshopper - IndC - 01-09-2026.xlsx
@@ -24,7 +24,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="11">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -64,11 +64,6 @@
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00B06A00"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <color rgb="008A8A8A"/>
       <sz val="10"/>
     </font>
     <font>
@@ -182,7 +177,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -218,16 +213,13 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -254,7 +246,7 @@
     <xf numFmtId="0" fontId="4" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
@@ -262,7 +254,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -2245,12 +2237,16 @@
       <c r="M19" s="7" t="inlineStr"/>
       <c r="N19" s="8" t="inlineStr"/>
       <c r="O19" s="10" t="inlineStr"/>
-      <c r="P19" s="13" t="inlineStr">
-        <is>
-          <t>À qualifier</t>
-        </is>
-      </c>
-      <c r="Q19" s="10" t="inlineStr"/>
+      <c r="P19" s="11" t="inlineStr">
+        <is>
+          <t>Compétence</t>
+        </is>
+      </c>
+      <c r="Q19" s="10" t="inlineStr">
+        <is>
+          <t>RH-23</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
@@ -2846,12 +2842,12 @@
           <t>REF-025</t>
         </is>
       </c>
-      <c r="C29" s="14" t="inlineStr">
+      <c r="C29" s="13" t="inlineStr">
         <is>
           <t>2 – Environnement et principes Grasshopper</t>
         </is>
       </c>
-      <c r="D29" s="14" t="inlineStr">
+      <c r="D29" s="13" t="inlineStr">
         <is>
           <t>Principes et interface Grasshopper</t>
         </is>
@@ -2911,12 +2907,12 @@
           <t>REF-026</t>
         </is>
       </c>
-      <c r="C30" s="14" t="inlineStr">
+      <c r="C30" s="13" t="inlineStr">
         <is>
           <t>2 – Environnement et principes Grasshopper</t>
         </is>
       </c>
-      <c r="D30" s="14" t="inlineStr">
+      <c r="D30" s="13" t="inlineStr">
         <is>
           <t>Principes et interface Grasshopper</t>
         </is>
@@ -2976,12 +2972,12 @@
           <t>REF-027</t>
         </is>
       </c>
-      <c r="C31" s="14" t="inlineStr">
+      <c r="C31" s="13" t="inlineStr">
         <is>
           <t>2 – Environnement et principes Grasshopper</t>
         </is>
       </c>
-      <c r="D31" s="14" t="inlineStr">
+      <c r="D31" s="13" t="inlineStr">
         <is>
           <t>Principes et interface Grasshopper</t>
         </is>
@@ -3028,7 +3024,7 @@
       </c>
       <c r="Q31" s="10" t="inlineStr">
         <is>
-          <t>A-01, A-03, A-05</t>
+          <t>A-01, A-03, A-05, C-01</t>
         </is>
       </c>
     </row>
@@ -3041,12 +3037,12 @@
           <t>REF-028</t>
         </is>
       </c>
-      <c r="C32" s="14" t="inlineStr">
+      <c r="C32" s="13" t="inlineStr">
         <is>
           <t>2 – Environnement et principes Grasshopper</t>
         </is>
       </c>
-      <c r="D32" s="14" t="inlineStr">
+      <c r="D32" s="13" t="inlineStr">
         <is>
           <t>Principes et interface Grasshopper</t>
         </is>
@@ -3106,12 +3102,12 @@
           <t>REF-029</t>
         </is>
       </c>
-      <c r="C33" s="14" t="inlineStr">
+      <c r="C33" s="13" t="inlineStr">
         <is>
           <t>2 – Environnement et principes Grasshopper</t>
         </is>
       </c>
-      <c r="D33" s="14" t="inlineStr">
+      <c r="D33" s="13" t="inlineStr">
         <is>
           <t>Écosystème de plugins</t>
         </is>
@@ -3171,12 +3167,12 @@
           <t>REF-030</t>
         </is>
       </c>
-      <c r="C34" s="14" t="inlineStr">
+      <c r="C34" s="13" t="inlineStr">
         <is>
           <t>2 – Environnement et principes Grasshopper</t>
         </is>
       </c>
-      <c r="D34" s="14" t="inlineStr">
+      <c r="D34" s="13" t="inlineStr">
         <is>
           <t>Écosystème de plugins</t>
         </is>
@@ -3236,12 +3232,12 @@
           <t>REF-031</t>
         </is>
       </c>
-      <c r="C35" s="14" t="inlineStr">
+      <c r="C35" s="13" t="inlineStr">
         <is>
           <t>2 – Environnement et principes Grasshopper</t>
         </is>
       </c>
-      <c r="D35" s="14" t="inlineStr">
+      <c r="D35" s="13" t="inlineStr">
         <is>
           <t>Écosystème de plugins</t>
         </is>
@@ -3301,12 +3297,12 @@
           <t>REF-032</t>
         </is>
       </c>
-      <c r="C36" s="14" t="inlineStr">
+      <c r="C36" s="13" t="inlineStr">
         <is>
           <t>2 – Environnement et principes Grasshopper</t>
         </is>
       </c>
-      <c r="D36" s="14" t="inlineStr">
+      <c r="D36" s="13" t="inlineStr">
         <is>
           <t>Écosystème de plugins</t>
         </is>
@@ -3366,12 +3362,12 @@
           <t>REF-033</t>
         </is>
       </c>
-      <c r="C37" s="14" t="inlineStr">
+      <c r="C37" s="13" t="inlineStr">
         <is>
           <t>2 – Environnement et principes Grasshopper</t>
         </is>
       </c>
-      <c r="D37" s="14" t="inlineStr">
+      <c r="D37" s="13" t="inlineStr">
         <is>
           <t>Écosystème de plugins</t>
         </is>
@@ -3431,12 +3427,12 @@
           <t>REF-034</t>
         </is>
       </c>
-      <c r="C38" s="14" t="inlineStr">
+      <c r="C38" s="13" t="inlineStr">
         <is>
           <t>2 – Environnement et principes Grasshopper</t>
         </is>
       </c>
-      <c r="D38" s="14" t="inlineStr">
+      <c r="D38" s="13" t="inlineStr">
         <is>
           <t>Écosystème de plugins</t>
         </is>
@@ -3496,12 +3492,12 @@
           <t>REF-035</t>
         </is>
       </c>
-      <c r="C39" s="14" t="inlineStr">
+      <c r="C39" s="13" t="inlineStr">
         <is>
           <t>2 – Environnement et principes Grasshopper</t>
         </is>
       </c>
-      <c r="D39" s="14" t="inlineStr">
+      <c r="D39" s="13" t="inlineStr">
         <is>
           <t>Écosystème de plugins</t>
         </is>
@@ -3561,12 +3557,12 @@
           <t>REF-036</t>
         </is>
       </c>
-      <c r="C40" s="14" t="inlineStr">
+      <c r="C40" s="13" t="inlineStr">
         <is>
           <t>2 – Environnement et principes Grasshopper</t>
         </is>
       </c>
-      <c r="D40" s="14" t="inlineStr">
+      <c r="D40" s="13" t="inlineStr">
         <is>
           <t>Écosystème de plugins</t>
         </is>
@@ -3626,12 +3622,12 @@
           <t>REF-037</t>
         </is>
       </c>
-      <c r="C41" s="14" t="inlineStr">
+      <c r="C41" s="13" t="inlineStr">
         <is>
           <t>2 – Environnement et principes Grasshopper</t>
         </is>
       </c>
-      <c r="D41" s="14" t="inlineStr">
+      <c r="D41" s="13" t="inlineStr">
         <is>
           <t>Écosystème de plugins</t>
         </is>
@@ -3691,12 +3687,12 @@
           <t>REF-038</t>
         </is>
       </c>
-      <c r="C42" s="14" t="inlineStr">
+      <c r="C42" s="13" t="inlineStr">
         <is>
           <t>2 – Environnement et principes Grasshopper</t>
         </is>
       </c>
-      <c r="D42" s="14" t="inlineStr">
+      <c r="D42" s="13" t="inlineStr">
         <is>
           <t>Écosystème de plugins</t>
         </is>
@@ -3756,12 +3752,12 @@
           <t>REF-039</t>
         </is>
       </c>
-      <c r="C43" s="14" t="inlineStr">
+      <c r="C43" s="13" t="inlineStr">
         <is>
           <t>2 – Environnement et principes Grasshopper</t>
         </is>
       </c>
-      <c r="D43" s="14" t="inlineStr">
+      <c r="D43" s="13" t="inlineStr">
         <is>
           <t>Écosystème de plugins</t>
         </is>
@@ -3821,12 +3817,12 @@
           <t>REF-040</t>
         </is>
       </c>
-      <c r="C44" s="15" t="inlineStr">
+      <c r="C44" s="14" t="inlineStr">
         <is>
           <t>3 – Données et logique</t>
         </is>
       </c>
-      <c r="D44" s="15" t="inlineStr">
+      <c r="D44" s="14" t="inlineStr">
         <is>
           <t>Types et conversion implicite</t>
         </is>
@@ -3886,12 +3882,12 @@
           <t>REF-041</t>
         </is>
       </c>
-      <c r="C45" s="15" t="inlineStr">
+      <c r="C45" s="14" t="inlineStr">
         <is>
           <t>3 – Données et logique</t>
         </is>
       </c>
-      <c r="D45" s="15" t="inlineStr">
+      <c r="D45" s="14" t="inlineStr">
         <is>
           <t>Types et conversion implicite</t>
         </is>
@@ -3951,12 +3947,12 @@
           <t>REF-145</t>
         </is>
       </c>
-      <c r="C46" s="15" t="inlineStr">
+      <c r="C46" s="14" t="inlineStr">
         <is>
           <t>3 – Données et logique</t>
         </is>
       </c>
-      <c r="D46" s="15" t="inlineStr">
+      <c r="D46" s="14" t="inlineStr">
         <is>
           <t>Types et conversion implicite</t>
         </is>
@@ -3996,12 +3992,16 @@
       <c r="M46" s="7" t="inlineStr"/>
       <c r="N46" s="8" t="inlineStr"/>
       <c r="O46" s="10" t="inlineStr"/>
-      <c r="P46" s="13" t="inlineStr">
-        <is>
-          <t>À qualifier</t>
-        </is>
-      </c>
-      <c r="Q46" s="10" t="inlineStr"/>
+      <c r="P46" s="11" t="inlineStr">
+        <is>
+          <t>Compétence</t>
+        </is>
+      </c>
+      <c r="Q46" s="10" t="inlineStr">
+        <is>
+          <t>A-51</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="7" t="n">
@@ -4012,12 +4012,12 @@
           <t>REF-042</t>
         </is>
       </c>
-      <c r="C47" s="15" t="inlineStr">
+      <c r="C47" s="14" t="inlineStr">
         <is>
           <t>3 – Données et logique</t>
         </is>
       </c>
-      <c r="D47" s="15" t="inlineStr">
+      <c r="D47" s="14" t="inlineStr">
         <is>
           <t>Listes</t>
         </is>
@@ -4077,12 +4077,12 @@
           <t>REF-043</t>
         </is>
       </c>
-      <c r="C48" s="15" t="inlineStr">
+      <c r="C48" s="14" t="inlineStr">
         <is>
           <t>3 – Données et logique</t>
         </is>
       </c>
-      <c r="D48" s="15" t="inlineStr">
+      <c r="D48" s="14" t="inlineStr">
         <is>
           <t>Listes</t>
         </is>
@@ -4129,7 +4129,7 @@
       </c>
       <c r="Q48" s="10" t="inlineStr">
         <is>
-          <t>A-10, A-12, A-18</t>
+          <t>A-10, A-12, A-18, B-01, B-02, B-08</t>
         </is>
       </c>
     </row>
@@ -4142,12 +4142,12 @@
           <t>REF-044</t>
         </is>
       </c>
-      <c r="C49" s="15" t="inlineStr">
+      <c r="C49" s="14" t="inlineStr">
         <is>
           <t>3 – Données et logique</t>
         </is>
       </c>
-      <c r="D49" s="15" t="inlineStr">
+      <c r="D49" s="14" t="inlineStr">
         <is>
           <t>Listes</t>
         </is>
@@ -4194,7 +4194,7 @@
       </c>
       <c r="Q49" s="10" t="inlineStr">
         <is>
-          <t>A-13</t>
+          <t>A-13, B-08, B-15</t>
         </is>
       </c>
     </row>
@@ -4207,12 +4207,12 @@
           <t>REF-045</t>
         </is>
       </c>
-      <c r="C50" s="15" t="inlineStr">
+      <c r="C50" s="14" t="inlineStr">
         <is>
           <t>3 – Données et logique</t>
         </is>
       </c>
-      <c r="D50" s="15" t="inlineStr">
+      <c r="D50" s="14" t="inlineStr">
         <is>
           <t>Listes</t>
         </is>
@@ -4259,7 +4259,7 @@
       </c>
       <c r="Q50" s="10" t="inlineStr">
         <is>
-          <t>A-14, A-15</t>
+          <t>A-14, A-15, B-13, B-15, C-09</t>
         </is>
       </c>
     </row>
@@ -4272,12 +4272,12 @@
           <t>REF-046</t>
         </is>
       </c>
-      <c r="C51" s="15" t="inlineStr">
+      <c r="C51" s="14" t="inlineStr">
         <is>
           <t>3 – Données et logique</t>
         </is>
       </c>
-      <c r="D51" s="15" t="inlineStr">
+      <c r="D51" s="14" t="inlineStr">
         <is>
           <t>Listes</t>
         </is>
@@ -4324,7 +4324,7 @@
       </c>
       <c r="Q51" s="10" t="inlineStr">
         <is>
-          <t>A-16</t>
+          <t>A-16, B-05, B-11, C-03</t>
         </is>
       </c>
     </row>
@@ -4337,12 +4337,12 @@
           <t>REF-047</t>
         </is>
       </c>
-      <c r="C52" s="15" t="inlineStr">
+      <c r="C52" s="14" t="inlineStr">
         <is>
           <t>3 – Données et logique</t>
         </is>
       </c>
-      <c r="D52" s="15" t="inlineStr">
+      <c r="D52" s="14" t="inlineStr">
         <is>
           <t>Listes</t>
         </is>
@@ -4389,7 +4389,7 @@
       </c>
       <c r="Q52" s="10" t="inlineStr">
         <is>
-          <t>A-10, A-13</t>
+          <t>A-10, A-13, B-01, B-02, B-08, C-03</t>
         </is>
       </c>
     </row>
@@ -4402,12 +4402,12 @@
           <t>REF-048</t>
         </is>
       </c>
-      <c r="C53" s="15" t="inlineStr">
+      <c r="C53" s="14" t="inlineStr">
         <is>
           <t>3 – Données et logique</t>
         </is>
       </c>
-      <c r="D53" s="15" t="inlineStr">
+      <c r="D53" s="14" t="inlineStr">
         <is>
           <t>Arbres de données</t>
         </is>
@@ -4467,12 +4467,12 @@
           <t>REF-049</t>
         </is>
       </c>
-      <c r="C54" s="15" t="inlineStr">
+      <c r="C54" s="14" t="inlineStr">
         <is>
           <t>3 – Données et logique</t>
         </is>
       </c>
-      <c r="D54" s="15" t="inlineStr">
+      <c r="D54" s="14" t="inlineStr">
         <is>
           <t>Arbres de données</t>
         </is>
@@ -4519,7 +4519,7 @@
       </c>
       <c r="Q54" s="10" t="inlineStr">
         <is>
-          <t>A-20</t>
+          <t>A-20, B-04, B-10, B-17, C-02</t>
         </is>
       </c>
     </row>
@@ -4532,12 +4532,12 @@
           <t>REF-050</t>
         </is>
       </c>
-      <c r="C55" s="15" t="inlineStr">
+      <c r="C55" s="14" t="inlineStr">
         <is>
           <t>3 – Données et logique</t>
         </is>
       </c>
-      <c r="D55" s="15" t="inlineStr">
+      <c r="D55" s="14" t="inlineStr">
         <is>
           <t>Arbres de données</t>
         </is>
@@ -4597,12 +4597,12 @@
           <t>REF-051</t>
         </is>
       </c>
-      <c r="C56" s="15" t="inlineStr">
+      <c r="C56" s="14" t="inlineStr">
         <is>
           <t>3 – Données et logique</t>
         </is>
       </c>
-      <c r="D56" s="15" t="inlineStr">
+      <c r="D56" s="14" t="inlineStr">
         <is>
           <t>Arbres de données</t>
         </is>
@@ -4662,12 +4662,12 @@
           <t>REF-052</t>
         </is>
       </c>
-      <c r="C57" s="15" t="inlineStr">
+      <c r="C57" s="14" t="inlineStr">
         <is>
           <t>3 – Données et logique</t>
         </is>
       </c>
-      <c r="D57" s="15" t="inlineStr">
+      <c r="D57" s="14" t="inlineStr">
         <is>
           <t>Arbres de données</t>
         </is>
@@ -4727,12 +4727,12 @@
           <t>REF-053</t>
         </is>
       </c>
-      <c r="C58" s="15" t="inlineStr">
+      <c r="C58" s="14" t="inlineStr">
         <is>
           <t>3 – Données et logique</t>
         </is>
       </c>
-      <c r="D58" s="15" t="inlineStr">
+      <c r="D58" s="14" t="inlineStr">
         <is>
           <t>Comportements implicites</t>
         </is>
@@ -4771,19 +4771,19 @@
       <c r="L58" s="8" t="inlineStr"/>
       <c r="M58" s="7" t="inlineStr"/>
       <c r="N58" s="8" t="inlineStr"/>
-      <c r="O58" s="16" t="inlineStr">
+      <c r="O58" s="15" t="inlineStr">
         <is>
           <t>⚠ Vérifié dans Rhino 8 le 26/08/2026 : la correspondance PAR DÉFAUT de Grasshopper n'est pas la troncature sur la liste la plus courte, mais la correspondance sur la liste la plus LONGUE, la liste courte étant prolongée par répétition de son dernier élément. Une liste de 10 et une liste de 4 dans une Addition produisent 10 résultats, pas 4. Le mode Shortest List existe mais doit être demandé explicitement par clic droit. L'intitulé de cette notion est donc à corriger.</t>
         </is>
       </c>
-      <c r="P58" s="12" t="inlineStr">
-        <is>
-          <t>Connaissance</t>
+      <c r="P58" s="11" t="inlineStr">
+        <is>
+          <t>Compétence</t>
         </is>
       </c>
       <c r="Q58" s="10" t="inlineStr">
         <is>
-          <t>A-24</t>
+          <t>A-24, B-03</t>
         </is>
       </c>
     </row>
@@ -4796,12 +4796,12 @@
           <t>REF-054</t>
         </is>
       </c>
-      <c r="C59" s="15" t="inlineStr">
+      <c r="C59" s="14" t="inlineStr">
         <is>
           <t>3 – Données et logique</t>
         </is>
       </c>
-      <c r="D59" s="15" t="inlineStr">
+      <c r="D59" s="14" t="inlineStr">
         <is>
           <t>Comportements implicites</t>
         </is>
@@ -4848,7 +4848,7 @@
       </c>
       <c r="Q59" s="10" t="inlineStr">
         <is>
-          <t>A-25</t>
+          <t>A-25, B-03</t>
         </is>
       </c>
     </row>
@@ -4861,12 +4861,12 @@
           <t>REF-055</t>
         </is>
       </c>
-      <c r="C60" s="15" t="inlineStr">
+      <c r="C60" s="14" t="inlineStr">
         <is>
           <t>3 – Données et logique</t>
         </is>
       </c>
-      <c r="D60" s="15" t="inlineStr">
+      <c r="D60" s="14" t="inlineStr">
         <is>
           <t>Comportements implicites</t>
         </is>
@@ -4926,12 +4926,12 @@
           <t>REF-056</t>
         </is>
       </c>
-      <c r="C61" s="15" t="inlineStr">
+      <c r="C61" s="14" t="inlineStr">
         <is>
           <t>3 – Données et logique</t>
         </is>
       </c>
-      <c r="D61" s="15" t="inlineStr">
+      <c r="D61" s="14" t="inlineStr">
         <is>
           <t>Comportements implicites</t>
         </is>
@@ -4991,12 +4991,12 @@
           <t>REF-057</t>
         </is>
       </c>
-      <c r="C62" s="15" t="inlineStr">
+      <c r="C62" s="14" t="inlineStr">
         <is>
           <t>3 – Données et logique</t>
         </is>
       </c>
-      <c r="D62" s="15" t="inlineStr">
+      <c r="D62" s="14" t="inlineStr">
         <is>
           <t>Outils de texte</t>
         </is>
@@ -5043,7 +5043,7 @@
       </c>
       <c r="Q62" s="10" t="inlineStr">
         <is>
-          <t>A-27</t>
+          <t>A-27, B-14</t>
         </is>
       </c>
     </row>
@@ -5056,12 +5056,12 @@
           <t>REF-058</t>
         </is>
       </c>
-      <c r="C63" s="15" t="inlineStr">
+      <c r="C63" s="14" t="inlineStr">
         <is>
           <t>3 – Données et logique</t>
         </is>
       </c>
-      <c r="D63" s="15" t="inlineStr">
+      <c r="D63" s="14" t="inlineStr">
         <is>
           <t>Outils de texte</t>
         </is>
@@ -5121,12 +5121,12 @@
           <t>REF-144</t>
         </is>
       </c>
-      <c r="C64" s="15" t="inlineStr">
+      <c r="C64" s="14" t="inlineStr">
         <is>
           <t>3 – Données et logique</t>
         </is>
       </c>
-      <c r="D64" s="15" t="inlineStr">
+      <c r="D64" s="14" t="inlineStr">
         <is>
           <t>Outils de texte</t>
         </is>
@@ -5166,12 +5166,16 @@
       <c r="M64" s="7" t="inlineStr"/>
       <c r="N64" s="8" t="inlineStr"/>
       <c r="O64" s="10" t="inlineStr"/>
-      <c r="P64" s="13" t="inlineStr">
-        <is>
-          <t>À qualifier</t>
-        </is>
-      </c>
-      <c r="Q64" s="10" t="inlineStr"/>
+      <c r="P64" s="11" t="inlineStr">
+        <is>
+          <t>Compétence</t>
+        </is>
+      </c>
+      <c r="Q64" s="10" t="inlineStr">
+        <is>
+          <t>A-50</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="7" t="n">
@@ -5182,12 +5186,12 @@
           <t>REF-059</t>
         </is>
       </c>
-      <c r="C65" s="15" t="inlineStr">
+      <c r="C65" s="14" t="inlineStr">
         <is>
           <t>3 – Données et logique</t>
         </is>
       </c>
-      <c r="D65" s="15" t="inlineStr">
+      <c r="D65" s="14" t="inlineStr">
         <is>
           <t>Portes logiques</t>
         </is>
@@ -5247,12 +5251,12 @@
           <t>REF-060</t>
         </is>
       </c>
-      <c r="C66" s="15" t="inlineStr">
+      <c r="C66" s="14" t="inlineStr">
         <is>
           <t>3 – Données et logique</t>
         </is>
       </c>
-      <c r="D66" s="15" t="inlineStr">
+      <c r="D66" s="14" t="inlineStr">
         <is>
           <t>Portes logiques</t>
         </is>
@@ -5299,7 +5303,7 @@
       </c>
       <c r="Q66" s="10" t="inlineStr">
         <is>
-          <t>A-30</t>
+          <t>A-30, C-03</t>
         </is>
       </c>
     </row>
@@ -5312,12 +5316,12 @@
           <t>REF-061</t>
         </is>
       </c>
-      <c r="C67" s="15" t="inlineStr">
+      <c r="C67" s="14" t="inlineStr">
         <is>
           <t>3 – Données et logique</t>
         </is>
       </c>
-      <c r="D67" s="15" t="inlineStr">
+      <c r="D67" s="14" t="inlineStr">
         <is>
           <t>Portes logiques</t>
         </is>
@@ -5377,12 +5381,12 @@
           <t>REF-062</t>
         </is>
       </c>
-      <c r="C68" s="17" t="inlineStr">
+      <c r="C68" s="16" t="inlineStr">
         <is>
           <t>4 – Géométrie paramétrique</t>
         </is>
       </c>
-      <c r="D68" s="17" t="inlineStr">
+      <c r="D68" s="16" t="inlineStr">
         <is>
           <t>Géométrie vectorielle et filaire</t>
         </is>
@@ -5442,12 +5446,12 @@
           <t>REF-063</t>
         </is>
       </c>
-      <c r="C69" s="17" t="inlineStr">
+      <c r="C69" s="16" t="inlineStr">
         <is>
           <t>4 – Géométrie paramétrique</t>
         </is>
       </c>
-      <c r="D69" s="17" t="inlineStr">
+      <c r="D69" s="16" t="inlineStr">
         <is>
           <t>Géométrie vectorielle et filaire</t>
         </is>
@@ -5494,7 +5498,7 @@
       </c>
       <c r="Q69" s="10" t="inlineStr">
         <is>
-          <t>A-34, A-36</t>
+          <t>A-34, A-36, B-05</t>
         </is>
       </c>
     </row>
@@ -5507,12 +5511,12 @@
           <t>REF-064</t>
         </is>
       </c>
-      <c r="C70" s="17" t="inlineStr">
+      <c r="C70" s="16" t="inlineStr">
         <is>
           <t>4 – Géométrie paramétrique</t>
         </is>
       </c>
-      <c r="D70" s="17" t="inlineStr">
+      <c r="D70" s="16" t="inlineStr">
         <is>
           <t>Géométrie vectorielle et filaire</t>
         </is>
@@ -5559,7 +5563,7 @@
       </c>
       <c r="Q70" s="10" t="inlineStr">
         <is>
-          <t>A-35</t>
+          <t>A-35, B-02, B-11, B-16, C-06</t>
         </is>
       </c>
     </row>
@@ -5572,12 +5576,12 @@
           <t>REF-065</t>
         </is>
       </c>
-      <c r="C71" s="17" t="inlineStr">
+      <c r="C71" s="16" t="inlineStr">
         <is>
           <t>4 – Géométrie paramétrique</t>
         </is>
       </c>
-      <c r="D71" s="17" t="inlineStr">
+      <c r="D71" s="16" t="inlineStr">
         <is>
           <t>Plan paramétrique</t>
         </is>
@@ -5637,12 +5641,12 @@
           <t>REF-066</t>
         </is>
       </c>
-      <c r="C72" s="17" t="inlineStr">
+      <c r="C72" s="16" t="inlineStr">
         <is>
           <t>4 – Géométrie paramétrique</t>
         </is>
       </c>
-      <c r="D72" s="17" t="inlineStr">
+      <c r="D72" s="16" t="inlineStr">
         <is>
           <t>Plan paramétrique</t>
         </is>
@@ -5689,7 +5693,7 @@
       </c>
       <c r="Q72" s="10" t="inlineStr">
         <is>
-          <t>GP-01, GP-05</t>
+          <t>B-14, GP-01, GP-05</t>
         </is>
       </c>
     </row>
@@ -5702,12 +5706,12 @@
           <t>REF-146</t>
         </is>
       </c>
-      <c r="C73" s="17" t="inlineStr">
+      <c r="C73" s="16" t="inlineStr">
         <is>
           <t>4 – Géométrie paramétrique</t>
         </is>
       </c>
-      <c r="D73" s="17" t="inlineStr">
+      <c r="D73" s="16" t="inlineStr">
         <is>
           <t>Plan paramétrique</t>
         </is>
@@ -5747,12 +5751,16 @@
       <c r="M73" s="7" t="inlineStr"/>
       <c r="N73" s="8" t="inlineStr"/>
       <c r="O73" s="10" t="inlineStr"/>
-      <c r="P73" s="13" t="inlineStr">
-        <is>
-          <t>À qualifier</t>
-        </is>
-      </c>
-      <c r="Q73" s="10" t="inlineStr"/>
+      <c r="P73" s="11" t="inlineStr">
+        <is>
+          <t>Compétence</t>
+        </is>
+      </c>
+      <c r="Q73" s="10" t="inlineStr">
+        <is>
+          <t>GP-09</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="7" t="n">
@@ -5763,12 +5771,12 @@
           <t>REF-067</t>
         </is>
       </c>
-      <c r="C74" s="17" t="inlineStr">
+      <c r="C74" s="16" t="inlineStr">
         <is>
           <t>4 – Géométrie paramétrique</t>
         </is>
       </c>
-      <c r="D74" s="17" t="inlineStr">
+      <c r="D74" s="16" t="inlineStr">
         <is>
           <t>Transformations et réseaux</t>
         </is>
@@ -5815,7 +5823,7 @@
       </c>
       <c r="Q74" s="10" t="inlineStr">
         <is>
-          <t>A-37, A-38, A-40</t>
+          <t>A-37, A-38, A-40, B-01, B-09, B-11, B-16</t>
         </is>
       </c>
     </row>
@@ -5828,12 +5836,12 @@
           <t>REF-068</t>
         </is>
       </c>
-      <c r="C75" s="17" t="inlineStr">
+      <c r="C75" s="16" t="inlineStr">
         <is>
           <t>4 – Géométrie paramétrique</t>
         </is>
       </c>
-      <c r="D75" s="17" t="inlineStr">
+      <c r="D75" s="16" t="inlineStr">
         <is>
           <t>Transformations et réseaux</t>
         </is>
@@ -5880,7 +5888,7 @@
       </c>
       <c r="Q75" s="10" t="inlineStr">
         <is>
-          <t>A-39</t>
+          <t>A-39, B-01, B-03, B-04, B-06, B-09, C-01, C-08, C-09</t>
         </is>
       </c>
     </row>
@@ -5893,12 +5901,12 @@
           <t>REF-149</t>
         </is>
       </c>
-      <c r="C76" s="17" t="inlineStr">
+      <c r="C76" s="16" t="inlineStr">
         <is>
           <t>4 – Géométrie paramétrique</t>
         </is>
       </c>
-      <c r="D76" s="17" t="inlineStr">
+      <c r="D76" s="16" t="inlineStr">
         <is>
           <t>Transformations et réseaux</t>
         </is>
@@ -5938,12 +5946,16 @@
       <c r="M76" s="7" t="inlineStr"/>
       <c r="N76" s="8" t="inlineStr"/>
       <c r="O76" s="10" t="inlineStr"/>
-      <c r="P76" s="13" t="inlineStr">
-        <is>
-          <t>À qualifier</t>
-        </is>
-      </c>
-      <c r="Q76" s="10" t="inlineStr"/>
+      <c r="P76" s="11" t="inlineStr">
+        <is>
+          <t>Compétence</t>
+        </is>
+      </c>
+      <c r="Q76" s="10" t="inlineStr">
+        <is>
+          <t>GP-12</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="7" t="n">
@@ -5954,12 +5966,12 @@
           <t>REF-069</t>
         </is>
       </c>
-      <c r="C77" s="17" t="inlineStr">
+      <c r="C77" s="16" t="inlineStr">
         <is>
           <t>4 – Géométrie paramétrique</t>
         </is>
       </c>
-      <c r="D77" s="17" t="inlineStr">
+      <c r="D77" s="16" t="inlineStr">
         <is>
           <t>Surfaces et solides</t>
         </is>
@@ -6006,7 +6018,7 @@
       </c>
       <c r="Q77" s="10" t="inlineStr">
         <is>
-          <t>A-41, A-42</t>
+          <t>A-41, A-42, B-04, B-09, B-10, B-16, B-17, B-18, C-02, C-06, C-08, C-10</t>
         </is>
       </c>
     </row>
@@ -6019,12 +6031,12 @@
           <t>REF-070</t>
         </is>
       </c>
-      <c r="C78" s="17" t="inlineStr">
+      <c r="C78" s="16" t="inlineStr">
         <is>
           <t>4 – Géométrie paramétrique</t>
         </is>
       </c>
-      <c r="D78" s="17" t="inlineStr">
+      <c r="D78" s="16" t="inlineStr">
         <is>
           <t>Surfaces et solides</t>
         </is>
@@ -6071,7 +6083,7 @@
       </c>
       <c r="Q78" s="10" t="inlineStr">
         <is>
-          <t>A-43</t>
+          <t>A-43, B-06, B-07, C-05, C-07</t>
         </is>
       </c>
     </row>
@@ -6084,12 +6096,12 @@
           <t>REF-071</t>
         </is>
       </c>
-      <c r="C79" s="17" t="inlineStr">
+      <c r="C79" s="16" t="inlineStr">
         <is>
           <t>4 – Géométrie paramétrique</t>
         </is>
       </c>
-      <c r="D79" s="17" t="inlineStr">
+      <c r="D79" s="16" t="inlineStr">
         <is>
           <t>Surfaces et solides</t>
         </is>
@@ -6136,7 +6148,7 @@
       </c>
       <c r="Q79" s="10" t="inlineStr">
         <is>
-          <t>A-44, A-45</t>
+          <t>A-44, A-45, B-06</t>
         </is>
       </c>
     </row>
@@ -6149,12 +6161,12 @@
           <t>REF-072</t>
         </is>
       </c>
-      <c r="C80" s="17" t="inlineStr">
+      <c r="C80" s="16" t="inlineStr">
         <is>
           <t>4 – Géométrie paramétrique</t>
         </is>
       </c>
-      <c r="D80" s="17" t="inlineStr">
+      <c r="D80" s="16" t="inlineStr">
         <is>
           <t>Surfaces et solides</t>
         </is>
@@ -6201,7 +6213,7 @@
       </c>
       <c r="Q80" s="10" t="inlineStr">
         <is>
-          <t>A-46</t>
+          <t>A-46, B-07, C-07</t>
         </is>
       </c>
     </row>
@@ -6214,12 +6226,12 @@
           <t>REF-073</t>
         </is>
       </c>
-      <c r="C81" s="17" t="inlineStr">
+      <c r="C81" s="16" t="inlineStr">
         <is>
           <t>4 – Géométrie paramétrique</t>
         </is>
       </c>
-      <c r="D81" s="17" t="inlineStr">
+      <c r="D81" s="16" t="inlineStr">
         <is>
           <t>Synthèse géométrie</t>
         </is>
@@ -6279,12 +6291,12 @@
           <t>REF-147</t>
         </is>
       </c>
-      <c r="C82" s="17" t="inlineStr">
+      <c r="C82" s="16" t="inlineStr">
         <is>
           <t>4 – Géométrie paramétrique</t>
         </is>
       </c>
-      <c r="D82" s="17" t="inlineStr">
+      <c r="D82" s="16" t="inlineStr">
         <is>
           <t>Synthèse géométrie</t>
         </is>
@@ -6324,12 +6336,16 @@
       <c r="M82" s="7" t="inlineStr"/>
       <c r="N82" s="8" t="inlineStr"/>
       <c r="O82" s="10" t="inlineStr"/>
-      <c r="P82" s="13" t="inlineStr">
-        <is>
-          <t>À qualifier</t>
-        </is>
-      </c>
-      <c r="Q82" s="10" t="inlineStr"/>
+      <c r="P82" s="12" t="inlineStr">
+        <is>
+          <t>Connaissance</t>
+        </is>
+      </c>
+      <c r="Q82" s="10" t="inlineStr">
+        <is>
+          <t>GP-10</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="7" t="n">
@@ -6340,12 +6356,12 @@
           <t>REF-148</t>
         </is>
       </c>
-      <c r="C83" s="17" t="inlineStr">
+      <c r="C83" s="16" t="inlineStr">
         <is>
           <t>4 – Géométrie paramétrique</t>
         </is>
       </c>
-      <c r="D83" s="17" t="inlineStr">
+      <c r="D83" s="16" t="inlineStr">
         <is>
           <t>Synthèse géométrie</t>
         </is>
@@ -6385,12 +6401,16 @@
       <c r="M83" s="7" t="inlineStr"/>
       <c r="N83" s="8" t="inlineStr"/>
       <c r="O83" s="10" t="inlineStr"/>
-      <c r="P83" s="13" t="inlineStr">
-        <is>
-          <t>À qualifier</t>
-        </is>
-      </c>
-      <c r="Q83" s="10" t="inlineStr"/>
+      <c r="P83" s="11" t="inlineStr">
+        <is>
+          <t>Compétence</t>
+        </is>
+      </c>
+      <c r="Q83" s="10" t="inlineStr">
+        <is>
+          <t>GP-11</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="7" t="n">
@@ -6401,12 +6421,12 @@
           <t>REF-074</t>
         </is>
       </c>
-      <c r="C84" s="17" t="inlineStr">
+      <c r="C84" s="16" t="inlineStr">
         <is>
           <t>4 – Géométrie paramétrique</t>
         </is>
       </c>
-      <c r="D84" s="17" t="inlineStr">
+      <c r="D84" s="16" t="inlineStr">
         <is>
           <t>Maillages et SubD</t>
         </is>
@@ -6453,7 +6473,7 @@
       </c>
       <c r="Q84" s="10" t="inlineStr">
         <is>
-          <t>GP-03, GP-06</t>
+          <t>C-02, C-06, GP-03, GP-06</t>
         </is>
       </c>
     </row>
@@ -6466,12 +6486,12 @@
           <t>REF-075</t>
         </is>
       </c>
-      <c r="C85" s="17" t="inlineStr">
+      <c r="C85" s="16" t="inlineStr">
         <is>
           <t>4 – Géométrie paramétrique</t>
         </is>
       </c>
-      <c r="D85" s="17" t="inlineStr">
+      <c r="D85" s="16" t="inlineStr">
         <is>
           <t>Maillages et SubD</t>
         </is>
@@ -6531,12 +6551,12 @@
           <t>REF-076</t>
         </is>
       </c>
-      <c r="C86" s="17" t="inlineStr">
+      <c r="C86" s="16" t="inlineStr">
         <is>
           <t>4 – Géométrie paramétrique</t>
         </is>
       </c>
-      <c r="D86" s="17" t="inlineStr">
+      <c r="D86" s="16" t="inlineStr">
         <is>
           <t>Maillages et SubD</t>
         </is>
@@ -6596,12 +6616,12 @@
           <t>REF-077</t>
         </is>
       </c>
-      <c r="C87" s="17" t="inlineStr">
+      <c r="C87" s="16" t="inlineStr">
         <is>
           <t>4 – Géométrie paramétrique</t>
         </is>
       </c>
-      <c r="D87" s="17" t="inlineStr">
+      <c r="D87" s="16" t="inlineStr">
         <is>
           <t>Maillages et SubD</t>
         </is>
@@ -6661,12 +6681,12 @@
           <t>REF-078</t>
         </is>
       </c>
-      <c r="C88" s="17" t="inlineStr">
+      <c r="C88" s="16" t="inlineStr">
         <is>
           <t>4 – Géométrie paramétrique</t>
         </is>
       </c>
-      <c r="D88" s="17" t="inlineStr">
+      <c r="D88" s="16" t="inlineStr">
         <is>
           <t>Maillages et SubD</t>
         </is>
@@ -6726,12 +6746,12 @@
           <t>REF-079</t>
         </is>
       </c>
-      <c r="C89" s="18" t="inlineStr">
+      <c r="C89" s="17" t="inlineStr">
         <is>
           <t>5 – Mesures, quantitatifs et export</t>
         </is>
       </c>
-      <c r="D89" s="18" t="inlineStr">
+      <c r="D89" s="17" t="inlineStr">
         <is>
           <t>Mesures géométriques</t>
         </is>
@@ -6778,7 +6798,7 @@
       </c>
       <c r="Q89" s="10" t="inlineStr">
         <is>
-          <t>A-47</t>
+          <t>A-47, B-05, C-01, C-03, C-08</t>
         </is>
       </c>
     </row>
@@ -6791,12 +6811,12 @@
           <t>REF-080</t>
         </is>
       </c>
-      <c r="C90" s="18" t="inlineStr">
+      <c r="C90" s="17" t="inlineStr">
         <is>
           <t>5 – Mesures, quantitatifs et export</t>
         </is>
       </c>
-      <c r="D90" s="18" t="inlineStr">
+      <c r="D90" s="17" t="inlineStr">
         <is>
           <t>Mesures géométriques</t>
         </is>
@@ -6843,7 +6863,7 @@
       </c>
       <c r="Q90" s="10" t="inlineStr">
         <is>
-          <t>A-48</t>
+          <t>A-48, C-09</t>
         </is>
       </c>
     </row>
@@ -6856,12 +6876,12 @@
           <t>REF-081</t>
         </is>
       </c>
-      <c r="C91" s="18" t="inlineStr">
+      <c r="C91" s="17" t="inlineStr">
         <is>
           <t>5 – Mesures, quantitatifs et export</t>
         </is>
       </c>
-      <c r="D91" s="18" t="inlineStr">
+      <c r="D91" s="17" t="inlineStr">
         <is>
           <t>Mesures géométriques</t>
         </is>
@@ -6908,7 +6928,7 @@
       </c>
       <c r="Q91" s="10" t="inlineStr">
         <is>
-          <t>A-49</t>
+          <t>A-49, B-14, C-08</t>
         </is>
       </c>
     </row>
@@ -6921,12 +6941,12 @@
           <t>REF-082</t>
         </is>
       </c>
-      <c r="C92" s="18" t="inlineStr">
+      <c r="C92" s="17" t="inlineStr">
         <is>
           <t>5 – Mesures, quantitatifs et export</t>
         </is>
       </c>
-      <c r="D92" s="18" t="inlineStr">
+      <c r="D92" s="17" t="inlineStr">
         <is>
           <t>Quantitatifs et chiffrage</t>
         </is>
@@ -6973,7 +6993,7 @@
       </c>
       <c r="Q92" s="10" t="inlineStr">
         <is>
-          <t>QT-01</t>
+          <t>B-12, B-13, B-15, C-04, C-05, C-07, C-11, QT-01</t>
         </is>
       </c>
     </row>
@@ -6986,12 +7006,12 @@
           <t>REF-083</t>
         </is>
       </c>
-      <c r="C93" s="18" t="inlineStr">
+      <c r="C93" s="17" t="inlineStr">
         <is>
           <t>5 – Mesures, quantitatifs et export</t>
         </is>
       </c>
-      <c r="D93" s="18" t="inlineStr">
+      <c r="D93" s="17" t="inlineStr">
         <is>
           <t>Quantitatifs et chiffrage</t>
         </is>
@@ -7038,7 +7058,7 @@
       </c>
       <c r="Q93" s="10" t="inlineStr">
         <is>
-          <t>QT-02, QT-06</t>
+          <t>B-12, C-04, QT-02, QT-06</t>
         </is>
       </c>
     </row>
@@ -7051,12 +7071,12 @@
           <t>REF-084</t>
         </is>
       </c>
-      <c r="C94" s="18" t="inlineStr">
+      <c r="C94" s="17" t="inlineStr">
         <is>
           <t>5 – Mesures, quantitatifs et export</t>
         </is>
       </c>
-      <c r="D94" s="18" t="inlineStr">
+      <c r="D94" s="17" t="inlineStr">
         <is>
           <t>Quantitatifs et chiffrage</t>
         </is>
@@ -7103,7 +7123,7 @@
       </c>
       <c r="Q94" s="10" t="inlineStr">
         <is>
-          <t>QT-01</t>
+          <t>C-04, QT-01</t>
         </is>
       </c>
     </row>
@@ -7116,12 +7136,12 @@
           <t>REF-085</t>
         </is>
       </c>
-      <c r="C95" s="18" t="inlineStr">
+      <c r="C95" s="17" t="inlineStr">
         <is>
           <t>5 – Mesures, quantitatifs et export</t>
         </is>
       </c>
-      <c r="D95" s="18" t="inlineStr">
+      <c r="D95" s="17" t="inlineStr">
         <is>
           <t>Export de données</t>
         </is>
@@ -7168,7 +7188,7 @@
       </c>
       <c r="Q95" s="10" t="inlineStr">
         <is>
-          <t>QT-03, QT-04</t>
+          <t>B-12, QT-03, QT-04</t>
         </is>
       </c>
     </row>
@@ -7181,12 +7201,12 @@
           <t>REF-086</t>
         </is>
       </c>
-      <c r="C96" s="18" t="inlineStr">
+      <c r="C96" s="17" t="inlineStr">
         <is>
           <t>5 – Mesures, quantitatifs et export</t>
         </is>
       </c>
-      <c r="D96" s="18" t="inlineStr">
+      <c r="D96" s="17" t="inlineStr">
         <is>
           <t>Export de données</t>
         </is>
@@ -7233,7 +7253,7 @@
       </c>
       <c r="Q96" s="10" t="inlineStr">
         <is>
-          <t>QT-03, QT-05</t>
+          <t>C-04, QT-03, QT-05</t>
         </is>
       </c>
     </row>
@@ -7246,12 +7266,12 @@
           <t>REF-087</t>
         </is>
       </c>
-      <c r="C97" s="18" t="inlineStr">
+      <c r="C97" s="17" t="inlineStr">
         <is>
           <t>5 – Mesures, quantitatifs et export</t>
         </is>
       </c>
-      <c r="D97" s="18" t="inlineStr">
+      <c r="D97" s="17" t="inlineStr">
         <is>
           <t>Export de données</t>
         </is>
@@ -7298,7 +7318,7 @@
       </c>
       <c r="Q97" s="10" t="inlineStr">
         <is>
-          <t>QT-03, QT-05</t>
+          <t>B-12, C-05, C-12, QT-03, QT-05</t>
         </is>
       </c>
     </row>
@@ -7311,12 +7331,12 @@
           <t>REF-088</t>
         </is>
       </c>
-      <c r="C98" s="19" t="inlineStr">
+      <c r="C98" s="18" t="inlineStr">
         <is>
           <t>6 – Méthode, performance et évènements</t>
         </is>
       </c>
-      <c r="D98" s="19" t="inlineStr">
+      <c r="D98" s="18" t="inlineStr">
         <is>
           <t>Organisation et performance</t>
         </is>
@@ -7376,12 +7396,12 @@
           <t>REF-089</t>
         </is>
       </c>
-      <c r="C99" s="19" t="inlineStr">
+      <c r="C99" s="18" t="inlineStr">
         <is>
           <t>6 – Méthode, performance et évènements</t>
         </is>
       </c>
-      <c r="D99" s="19" t="inlineStr">
+      <c r="D99" s="18" t="inlineStr">
         <is>
           <t>Organisation et performance</t>
         </is>
@@ -7441,12 +7461,12 @@
           <t>REF-150</t>
         </is>
       </c>
-      <c r="C100" s="19" t="inlineStr">
+      <c r="C100" s="18" t="inlineStr">
         <is>
           <t>6 – Méthode, performance et évènements</t>
         </is>
       </c>
-      <c r="D100" s="19" t="inlineStr">
+      <c r="D100" s="18" t="inlineStr">
         <is>
           <t>Organisation et performance</t>
         </is>
@@ -7486,12 +7506,16 @@
       <c r="M100" s="7" t="inlineStr"/>
       <c r="N100" s="8" t="inlineStr"/>
       <c r="O100" s="10" t="inlineStr"/>
-      <c r="P100" s="13" t="inlineStr">
-        <is>
-          <t>À qualifier</t>
-        </is>
-      </c>
-      <c r="Q100" s="10" t="inlineStr"/>
+      <c r="P100" s="11" t="inlineStr">
+        <is>
+          <t>Compétence</t>
+        </is>
+      </c>
+      <c r="Q100" s="10" t="inlineStr">
+        <is>
+          <t>MP-05</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="7" t="n">
@@ -7502,12 +7526,12 @@
           <t>REF-090</t>
         </is>
       </c>
-      <c r="C101" s="19" t="inlineStr">
+      <c r="C101" s="18" t="inlineStr">
         <is>
           <t>6 – Méthode, performance et évènements</t>
         </is>
       </c>
-      <c r="D101" s="19" t="inlineStr">
+      <c r="D101" s="18" t="inlineStr">
         <is>
           <t>Chronologie et évènements</t>
         </is>
@@ -7567,12 +7591,12 @@
           <t>REF-091</t>
         </is>
       </c>
-      <c r="C102" s="19" t="inlineStr">
+      <c r="C102" s="18" t="inlineStr">
         <is>
           <t>6 – Méthode, performance et évènements</t>
         </is>
       </c>
-      <c r="D102" s="19" t="inlineStr">
+      <c r="D102" s="18" t="inlineStr">
         <is>
           <t>Chronologie et évènements</t>
         </is>
@@ -7632,12 +7656,12 @@
           <t>REF-092</t>
         </is>
       </c>
-      <c r="C103" s="19" t="inlineStr">
+      <c r="C103" s="18" t="inlineStr">
         <is>
           <t>6 – Méthode, performance et évènements</t>
         </is>
       </c>
-      <c r="D103" s="19" t="inlineStr">
+      <c r="D103" s="18" t="inlineStr">
         <is>
           <t>Chronologie et évènements</t>
         </is>
@@ -7697,12 +7721,12 @@
           <t>REF-093</t>
         </is>
       </c>
-      <c r="C104" s="20" t="inlineStr">
+      <c r="C104" s="19" t="inlineStr">
         <is>
           <t>7 – Algorithmique avancée</t>
         </is>
       </c>
-      <c r="D104" s="20" t="inlineStr">
+      <c r="D104" s="19" t="inlineStr">
         <is>
           <t>Boucles et itération</t>
         </is>
@@ -7762,12 +7786,12 @@
           <t>REF-151</t>
         </is>
       </c>
-      <c r="C105" s="20" t="inlineStr">
+      <c r="C105" s="19" t="inlineStr">
         <is>
           <t>7 – Algorithmique avancée</t>
         </is>
       </c>
-      <c r="D105" s="20" t="inlineStr">
+      <c r="D105" s="19" t="inlineStr">
         <is>
           <t>Boucles et itération</t>
         </is>
@@ -7807,12 +7831,16 @@
       <c r="M105" s="7" t="inlineStr"/>
       <c r="N105" s="8" t="inlineStr"/>
       <c r="O105" s="10" t="inlineStr"/>
-      <c r="P105" s="13" t="inlineStr">
-        <is>
-          <t>À qualifier</t>
-        </is>
-      </c>
-      <c r="Q105" s="10" t="inlineStr"/>
+      <c r="P105" s="11" t="inlineStr">
+        <is>
+          <t>Compétence</t>
+        </is>
+      </c>
+      <c r="Q105" s="10" t="inlineStr">
+        <is>
+          <t>AV-04</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="7" t="n">
@@ -7823,12 +7851,12 @@
           <t>REF-152</t>
         </is>
       </c>
-      <c r="C106" s="20" t="inlineStr">
+      <c r="C106" s="19" t="inlineStr">
         <is>
           <t>7 – Algorithmique avancée</t>
         </is>
       </c>
-      <c r="D106" s="20" t="inlineStr">
+      <c r="D106" s="19" t="inlineStr">
         <is>
           <t>Boucles et itération</t>
         </is>
@@ -7868,12 +7896,16 @@
       <c r="M106" s="7" t="inlineStr"/>
       <c r="N106" s="8" t="inlineStr"/>
       <c r="O106" s="10" t="inlineStr"/>
-      <c r="P106" s="13" t="inlineStr">
-        <is>
-          <t>À qualifier</t>
-        </is>
-      </c>
-      <c r="Q106" s="10" t="inlineStr"/>
+      <c r="P106" s="11" t="inlineStr">
+        <is>
+          <t>Compétence</t>
+        </is>
+      </c>
+      <c r="Q106" s="10" t="inlineStr">
+        <is>
+          <t>AV-05</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="7" t="n">
@@ -7884,12 +7916,12 @@
           <t>REF-094</t>
         </is>
       </c>
-      <c r="C107" s="20" t="inlineStr">
+      <c r="C107" s="19" t="inlineStr">
         <is>
           <t>7 – Algorithmique avancée</t>
         </is>
       </c>
-      <c r="D107" s="20" t="inlineStr">
+      <c r="D107" s="19" t="inlineStr">
         <is>
           <t>Simulation physique</t>
         </is>
@@ -7936,7 +7968,7 @@
       </c>
       <c r="Q107" s="10" t="inlineStr">
         <is>
-          <t>AV-02</t>
+          <t>AV-02, C-02</t>
         </is>
       </c>
     </row>
@@ -7949,12 +7981,12 @@
           <t>REF-155</t>
         </is>
       </c>
-      <c r="C108" s="20" t="inlineStr">
+      <c r="C108" s="19" t="inlineStr">
         <is>
           <t>7 – Algorithmique avancée</t>
         </is>
       </c>
-      <c r="D108" s="20" t="inlineStr">
+      <c r="D108" s="19" t="inlineStr">
         <is>
           <t>Simulation physique</t>
         </is>
@@ -7994,12 +8026,16 @@
       <c r="M108" s="7" t="inlineStr"/>
       <c r="N108" s="8" t="inlineStr"/>
       <c r="O108" s="10" t="inlineStr"/>
-      <c r="P108" s="13" t="inlineStr">
-        <is>
-          <t>À qualifier</t>
-        </is>
-      </c>
-      <c r="Q108" s="10" t="inlineStr"/>
+      <c r="P108" s="11" t="inlineStr">
+        <is>
+          <t>Compétence</t>
+        </is>
+      </c>
+      <c r="Q108" s="10" t="inlineStr">
+        <is>
+          <t>AV-08</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="7" t="n">
@@ -8010,12 +8046,12 @@
           <t>REF-156</t>
         </is>
       </c>
-      <c r="C109" s="20" t="inlineStr">
+      <c r="C109" s="19" t="inlineStr">
         <is>
           <t>7 – Algorithmique avancée</t>
         </is>
       </c>
-      <c r="D109" s="20" t="inlineStr">
+      <c r="D109" s="19" t="inlineStr">
         <is>
           <t>Simulation physique</t>
         </is>
@@ -8055,12 +8091,16 @@
       <c r="M109" s="7" t="inlineStr"/>
       <c r="N109" s="8" t="inlineStr"/>
       <c r="O109" s="10" t="inlineStr"/>
-      <c r="P109" s="13" t="inlineStr">
-        <is>
-          <t>À qualifier</t>
-        </is>
-      </c>
-      <c r="Q109" s="10" t="inlineStr"/>
+      <c r="P109" s="12" t="inlineStr">
+        <is>
+          <t>Connaissance</t>
+        </is>
+      </c>
+      <c r="Q109" s="10" t="inlineStr">
+        <is>
+          <t>AV-09</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="7" t="n">
@@ -8071,12 +8111,12 @@
           <t>REF-095</t>
         </is>
       </c>
-      <c r="C110" s="20" t="inlineStr">
+      <c r="C110" s="19" t="inlineStr">
         <is>
           <t>7 – Algorithmique avancée</t>
         </is>
       </c>
-      <c r="D110" s="20" t="inlineStr">
+      <c r="D110" s="19" t="inlineStr">
         <is>
           <t>Design génératif</t>
         </is>
@@ -8123,7 +8163,7 @@
       </c>
       <c r="Q110" s="10" t="inlineStr">
         <is>
-          <t>AV-03</t>
+          <t>AV-03, C-01, C-10</t>
         </is>
       </c>
     </row>
@@ -8136,12 +8176,12 @@
           <t>REF-153</t>
         </is>
       </c>
-      <c r="C111" s="20" t="inlineStr">
+      <c r="C111" s="19" t="inlineStr">
         <is>
           <t>7 – Algorithmique avancée</t>
         </is>
       </c>
-      <c r="D111" s="20" t="inlineStr">
+      <c r="D111" s="19" t="inlineStr">
         <is>
           <t>Design génératif</t>
         </is>
@@ -8181,12 +8221,16 @@
       <c r="M111" s="7" t="inlineStr"/>
       <c r="N111" s="8" t="inlineStr"/>
       <c r="O111" s="10" t="inlineStr"/>
-      <c r="P111" s="13" t="inlineStr">
-        <is>
-          <t>À qualifier</t>
-        </is>
-      </c>
-      <c r="Q111" s="10" t="inlineStr"/>
+      <c r="P111" s="12" t="inlineStr">
+        <is>
+          <t>Connaissance</t>
+        </is>
+      </c>
+      <c r="Q111" s="10" t="inlineStr">
+        <is>
+          <t>AV-06</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="7" t="n">
@@ -8197,12 +8241,12 @@
           <t>REF-154</t>
         </is>
       </c>
-      <c r="C112" s="20" t="inlineStr">
+      <c r="C112" s="19" t="inlineStr">
         <is>
           <t>7 – Algorithmique avancée</t>
         </is>
       </c>
-      <c r="D112" s="20" t="inlineStr">
+      <c r="D112" s="19" t="inlineStr">
         <is>
           <t>Design génératif</t>
         </is>
@@ -8242,12 +8286,16 @@
       <c r="M112" s="7" t="inlineStr"/>
       <c r="N112" s="8" t="inlineStr"/>
       <c r="O112" s="10" t="inlineStr"/>
-      <c r="P112" s="13" t="inlineStr">
-        <is>
-          <t>À qualifier</t>
-        </is>
-      </c>
-      <c r="Q112" s="10" t="inlineStr"/>
+      <c r="P112" s="11" t="inlineStr">
+        <is>
+          <t>Compétence</t>
+        </is>
+      </c>
+      <c r="Q112" s="10" t="inlineStr">
+        <is>
+          <t>AV-07</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="7" t="n">
@@ -8258,12 +8306,12 @@
           <t>REF-096</t>
         </is>
       </c>
-      <c r="C113" s="21" t="inlineStr">
+      <c r="C113" s="20" t="inlineStr">
         <is>
           <t>8 – Développement, scripting et API</t>
         </is>
       </c>
-      <c r="D113" s="21" t="inlineStr">
+      <c r="D113" s="20" t="inlineStr">
         <is>
           <t>Compilation et IDE</t>
         </is>
@@ -8323,12 +8371,12 @@
           <t>REF-097</t>
         </is>
       </c>
-      <c r="C114" s="21" t="inlineStr">
+      <c r="C114" s="20" t="inlineStr">
         <is>
           <t>8 – Développement, scripting et API</t>
         </is>
       </c>
-      <c r="D114" s="21" t="inlineStr">
+      <c r="D114" s="20" t="inlineStr">
         <is>
           <t>Compilation et IDE</t>
         </is>
@@ -8388,12 +8436,12 @@
           <t>REF-098</t>
         </is>
       </c>
-      <c r="C115" s="21" t="inlineStr">
+      <c r="C115" s="20" t="inlineStr">
         <is>
           <t>8 – Développement, scripting et API</t>
         </is>
       </c>
-      <c r="D115" s="21" t="inlineStr">
+      <c r="D115" s="20" t="inlineStr">
         <is>
           <t>Compilation et IDE</t>
         </is>
@@ -8453,12 +8501,12 @@
           <t>REF-099</t>
         </is>
       </c>
-      <c r="C116" s="21" t="inlineStr">
+      <c r="C116" s="20" t="inlineStr">
         <is>
           <t>8 – Développement, scripting et API</t>
         </is>
       </c>
-      <c r="D116" s="21" t="inlineStr">
+      <c r="D116" s="20" t="inlineStr">
         <is>
           <t>Compilation et IDE</t>
         </is>
@@ -8518,12 +8566,12 @@
           <t>REF-100</t>
         </is>
       </c>
-      <c r="C117" s="21" t="inlineStr">
+      <c r="C117" s="20" t="inlineStr">
         <is>
           <t>8 – Développement, scripting et API</t>
         </is>
       </c>
-      <c r="D117" s="21" t="inlineStr">
+      <c r="D117" s="20" t="inlineStr">
         <is>
           <t>Scripting dans Grasshopper</t>
         </is>
@@ -8583,12 +8631,12 @@
           <t>REF-101</t>
         </is>
       </c>
-      <c r="C118" s="21" t="inlineStr">
+      <c r="C118" s="20" t="inlineStr">
         <is>
           <t>8 – Développement, scripting et API</t>
         </is>
       </c>
-      <c r="D118" s="21" t="inlineStr">
+      <c r="D118" s="20" t="inlineStr">
         <is>
           <t>Scripting dans Grasshopper</t>
         </is>
@@ -8635,7 +8683,7 @@
       </c>
       <c r="Q118" s="10" t="inlineStr">
         <is>
-          <t>DV-02</t>
+          <t>B-17, C-09, DV-02</t>
         </is>
       </c>
     </row>
@@ -8648,12 +8696,12 @@
           <t>REF-102</t>
         </is>
       </c>
-      <c r="C119" s="21" t="inlineStr">
+      <c r="C119" s="20" t="inlineStr">
         <is>
           <t>8 – Développement, scripting et API</t>
         </is>
       </c>
-      <c r="D119" s="21" t="inlineStr">
+      <c r="D119" s="20" t="inlineStr">
         <is>
           <t>Scripting dans Grasshopper</t>
         </is>
@@ -8713,12 +8761,12 @@
           <t>REF-103</t>
         </is>
       </c>
-      <c r="C120" s="21" t="inlineStr">
+      <c r="C120" s="20" t="inlineStr">
         <is>
           <t>8 – Développement, scripting et API</t>
         </is>
       </c>
-      <c r="D120" s="21" t="inlineStr">
+      <c r="D120" s="20" t="inlineStr">
         <is>
           <t>API et librairies</t>
         </is>
@@ -8765,7 +8813,7 @@
       </c>
       <c r="Q120" s="10" t="inlineStr">
         <is>
-          <t>DV-02</t>
+          <t>B-18, DV-02</t>
         </is>
       </c>
     </row>
@@ -8778,12 +8826,12 @@
           <t>REF-104</t>
         </is>
       </c>
-      <c r="C121" s="21" t="inlineStr">
+      <c r="C121" s="20" t="inlineStr">
         <is>
           <t>8 – Développement, scripting et API</t>
         </is>
       </c>
-      <c r="D121" s="21" t="inlineStr">
+      <c r="D121" s="20" t="inlineStr">
         <is>
           <t>API et librairies</t>
         </is>
@@ -8843,12 +8891,12 @@
           <t>REF-105</t>
         </is>
       </c>
-      <c r="C122" s="21" t="inlineStr">
+      <c r="C122" s="20" t="inlineStr">
         <is>
           <t>8 – Développement, scripting et API</t>
         </is>
       </c>
-      <c r="D122" s="21" t="inlineStr">
+      <c r="D122" s="20" t="inlineStr">
         <is>
           <t>API et librairies</t>
         </is>
@@ -8908,12 +8956,12 @@
           <t>REF-106</t>
         </is>
       </c>
-      <c r="C123" s="22" t="inlineStr">
+      <c r="C123" s="21" t="inlineStr">
         <is>
           <t>9 – Interfaces, web et interopérabilité</t>
         </is>
       </c>
-      <c r="D123" s="22" t="inlineStr">
+      <c r="D123" s="21" t="inlineStr">
         <is>
           <t>Interfaces utilisateur</t>
         </is>
@@ -8960,7 +9008,7 @@
       </c>
       <c r="Q123" s="10" t="inlineStr">
         <is>
-          <t>WB-01</t>
+          <t>C-07, WB-01</t>
         </is>
       </c>
     </row>
@@ -8973,12 +9021,12 @@
           <t>REF-107</t>
         </is>
       </c>
-      <c r="C124" s="22" t="inlineStr">
+      <c r="C124" s="21" t="inlineStr">
         <is>
           <t>9 – Interfaces, web et interopérabilité</t>
         </is>
       </c>
-      <c r="D124" s="22" t="inlineStr">
+      <c r="D124" s="21" t="inlineStr">
         <is>
           <t>Interfaces utilisateur</t>
         </is>
@@ -9038,12 +9086,12 @@
           <t>REF-157</t>
         </is>
       </c>
-      <c r="C125" s="22" t="inlineStr">
+      <c r="C125" s="21" t="inlineStr">
         <is>
           <t>9 – Interfaces, web et interopérabilité</t>
         </is>
       </c>
-      <c r="D125" s="22" t="inlineStr">
+      <c r="D125" s="21" t="inlineStr">
         <is>
           <t>Interfaces utilisateur</t>
         </is>
@@ -9083,12 +9131,16 @@
       <c r="M125" s="7" t="inlineStr"/>
       <c r="N125" s="8" t="inlineStr"/>
       <c r="O125" s="10" t="inlineStr"/>
-      <c r="P125" s="13" t="inlineStr">
-        <is>
-          <t>À qualifier</t>
-        </is>
-      </c>
-      <c r="Q125" s="10" t="inlineStr"/>
+      <c r="P125" s="11" t="inlineStr">
+        <is>
+          <t>Compétence</t>
+        </is>
+      </c>
+      <c r="Q125" s="10" t="inlineStr">
+        <is>
+          <t>WB-08</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="7" t="n">
@@ -9099,12 +9151,12 @@
           <t>REF-108</t>
         </is>
       </c>
-      <c r="C126" s="22" t="inlineStr">
+      <c r="C126" s="21" t="inlineStr">
         <is>
           <t>9 – Interfaces, web et interopérabilité</t>
         </is>
       </c>
-      <c r="D126" s="22" t="inlineStr">
+      <c r="D126" s="21" t="inlineStr">
         <is>
           <t>Publication web</t>
         </is>
@@ -9164,12 +9216,12 @@
           <t>REF-109</t>
         </is>
       </c>
-      <c r="C127" s="22" t="inlineStr">
+      <c r="C127" s="21" t="inlineStr">
         <is>
           <t>9 – Interfaces, web et interopérabilité</t>
         </is>
       </c>
-      <c r="D127" s="22" t="inlineStr">
+      <c r="D127" s="21" t="inlineStr">
         <is>
           <t>Publication web</t>
         </is>
@@ -9229,12 +9281,12 @@
           <t>REF-110</t>
         </is>
       </c>
-      <c r="C128" s="22" t="inlineStr">
+      <c r="C128" s="21" t="inlineStr">
         <is>
           <t>9 – Interfaces, web et interopérabilité</t>
         </is>
       </c>
-      <c r="D128" s="22" t="inlineStr">
+      <c r="D128" s="21" t="inlineStr">
         <is>
           <t>Publication web</t>
         </is>
@@ -9294,12 +9346,12 @@
           <t>REF-111</t>
         </is>
       </c>
-      <c r="C129" s="22" t="inlineStr">
+      <c r="C129" s="21" t="inlineStr">
         <is>
           <t>9 – Interfaces, web et interopérabilité</t>
         </is>
       </c>
-      <c r="D129" s="22" t="inlineStr">
+      <c r="D129" s="21" t="inlineStr">
         <is>
           <t>Interopérabilité</t>
         </is>
@@ -9359,12 +9411,12 @@
           <t>REF-112</t>
         </is>
       </c>
-      <c r="C130" s="22" t="inlineStr">
+      <c r="C130" s="21" t="inlineStr">
         <is>
           <t>9 – Interfaces, web et interopérabilité</t>
         </is>
       </c>
-      <c r="D130" s="22" t="inlineStr">
+      <c r="D130" s="21" t="inlineStr">
         <is>
           <t>Interopérabilité</t>
         </is>
@@ -9424,12 +9476,12 @@
           <t>REF-158</t>
         </is>
       </c>
-      <c r="C131" s="22" t="inlineStr">
+      <c r="C131" s="21" t="inlineStr">
         <is>
           <t>9 – Interfaces, web et interopérabilité</t>
         </is>
       </c>
-      <c r="D131" s="22" t="inlineStr">
+      <c r="D131" s="21" t="inlineStr">
         <is>
           <t>Interopérabilité</t>
         </is>
@@ -9469,12 +9521,16 @@
       <c r="M131" s="7" t="inlineStr"/>
       <c r="N131" s="8" t="inlineStr"/>
       <c r="O131" s="10" t="inlineStr"/>
-      <c r="P131" s="13" t="inlineStr">
-        <is>
-          <t>À qualifier</t>
-        </is>
-      </c>
-      <c r="Q131" s="10" t="inlineStr"/>
+      <c r="P131" s="11" t="inlineStr">
+        <is>
+          <t>Compétence</t>
+        </is>
+      </c>
+      <c r="Q131" s="10" t="inlineStr">
+        <is>
+          <t>WB-09</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="7" t="n">
@@ -9485,12 +9541,12 @@
           <t>REF-113</t>
         </is>
       </c>
-      <c r="C132" s="23" t="inlineStr">
+      <c r="C132" s="22" t="inlineStr">
         <is>
           <t>10 – Aide à la fabrication</t>
         </is>
       </c>
-      <c r="D132" s="23" t="inlineStr">
+      <c r="D132" s="22" t="inlineStr">
         <is>
           <t>Imbrication</t>
         </is>
@@ -9537,7 +9593,7 @@
       </c>
       <c r="Q132" s="10" t="inlineStr">
         <is>
-          <t>FA-01</t>
+          <t>B-13, C-12, FA-01</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9606,12 @@
           <t>REF-114</t>
         </is>
       </c>
-      <c r="C133" s="23" t="inlineStr">
+      <c r="C133" s="22" t="inlineStr">
         <is>
           <t>10 – Aide à la fabrication</t>
         </is>
       </c>
-      <c r="D133" s="23" t="inlineStr">
+      <c r="D133" s="22" t="inlineStr">
         <is>
           <t>Imbrication</t>
         </is>
@@ -9602,7 +9658,7 @@
       </c>
       <c r="Q133" s="10" t="inlineStr">
         <is>
-          <t>FA-01, FA-04</t>
+          <t>C-12, FA-01, FA-04</t>
         </is>
       </c>
     </row>
@@ -9615,12 +9671,12 @@
           <t>REF-160</t>
         </is>
       </c>
-      <c r="C134" s="23" t="inlineStr">
+      <c r="C134" s="22" t="inlineStr">
         <is>
           <t>10 – Aide à la fabrication</t>
         </is>
       </c>
-      <c r="D134" s="23" t="inlineStr">
+      <c r="D134" s="22" t="inlineStr">
         <is>
           <t>Imbrication</t>
         </is>
@@ -9660,12 +9716,16 @@
       <c r="M134" s="7" t="inlineStr"/>
       <c r="N134" s="8" t="inlineStr"/>
       <c r="O134" s="10" t="inlineStr"/>
-      <c r="P134" s="13" t="inlineStr">
-        <is>
-          <t>À qualifier</t>
-        </is>
-      </c>
-      <c r="Q134" s="10" t="inlineStr"/>
+      <c r="P134" s="11" t="inlineStr">
+        <is>
+          <t>Compétence</t>
+        </is>
+      </c>
+      <c r="Q134" s="10" t="inlineStr">
+        <is>
+          <t>FA-06</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="7" t="n">
@@ -9676,12 +9736,12 @@
           <t>REF-115</t>
         </is>
       </c>
-      <c r="C135" s="23" t="inlineStr">
+      <c r="C135" s="22" t="inlineStr">
         <is>
           <t>10 – Aide à la fabrication</t>
         </is>
       </c>
-      <c r="D135" s="23" t="inlineStr">
+      <c r="D135" s="22" t="inlineStr">
         <is>
           <t>Déroulé et mise à plat</t>
         </is>
@@ -9728,7 +9788,7 @@
       </c>
       <c r="Q135" s="10" t="inlineStr">
         <is>
-          <t>FA-02</t>
+          <t>B-10, C-05, C-10, C-11, FA-02</t>
         </is>
       </c>
     </row>
@@ -9741,12 +9801,12 @@
           <t>REF-116</t>
         </is>
       </c>
-      <c r="C136" s="23" t="inlineStr">
+      <c r="C136" s="22" t="inlineStr">
         <is>
           <t>10 – Aide à la fabrication</t>
         </is>
       </c>
-      <c r="D136" s="23" t="inlineStr">
+      <c r="D136" s="22" t="inlineStr">
         <is>
           <t>Déroulé et mise à plat</t>
         </is>
@@ -9793,7 +9853,7 @@
       </c>
       <c r="Q136" s="10" t="inlineStr">
         <is>
-          <t>FA-02, FA-03</t>
+          <t>C-11, FA-02, FA-03</t>
         </is>
       </c>
     </row>
@@ -9806,12 +9866,12 @@
           <t>REF-159</t>
         </is>
       </c>
-      <c r="C137" s="23" t="inlineStr">
+      <c r="C137" s="22" t="inlineStr">
         <is>
           <t>10 – Aide à la fabrication</t>
         </is>
       </c>
-      <c r="D137" s="23" t="inlineStr">
+      <c r="D137" s="22" t="inlineStr">
         <is>
           <t>Déroulé et mise à plat</t>
         </is>
@@ -9851,12 +9911,16 @@
       <c r="M137" s="7" t="inlineStr"/>
       <c r="N137" s="8" t="inlineStr"/>
       <c r="O137" s="10" t="inlineStr"/>
-      <c r="P137" s="13" t="inlineStr">
-        <is>
-          <t>À qualifier</t>
-        </is>
-      </c>
-      <c r="Q137" s="10" t="inlineStr"/>
+      <c r="P137" s="12" t="inlineStr">
+        <is>
+          <t>Connaissance</t>
+        </is>
+      </c>
+      <c r="Q137" s="10" t="inlineStr">
+        <is>
+          <t>FA-05</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="7" t="n">
@@ -9867,12 +9931,12 @@
           <t>REF-117</t>
         </is>
       </c>
-      <c r="C138" s="24" t="inlineStr">
+      <c r="C138" s="23" t="inlineStr">
         <is>
           <t>11 – IA et assistance générative</t>
         </is>
       </c>
-      <c r="D138" s="24" t="inlineStr">
+      <c r="D138" s="23" t="inlineStr">
         <is>
           <t>Formuler et cadrer une demande</t>
         </is>
@@ -9932,12 +9996,12 @@
           <t>REF-118</t>
         </is>
       </c>
-      <c r="C139" s="24" t="inlineStr">
+      <c r="C139" s="23" t="inlineStr">
         <is>
           <t>11 – IA et assistance générative</t>
         </is>
       </c>
-      <c r="D139" s="24" t="inlineStr">
+      <c r="D139" s="23" t="inlineStr">
         <is>
           <t>Formuler et cadrer une demande</t>
         </is>
@@ -9997,12 +10061,12 @@
           <t>REF-119</t>
         </is>
       </c>
-      <c r="C140" s="24" t="inlineStr">
+      <c r="C140" s="23" t="inlineStr">
         <is>
           <t>11 – IA et assistance générative</t>
         </is>
       </c>
-      <c r="D140" s="24" t="inlineStr">
+      <c r="D140" s="23" t="inlineStr">
         <is>
           <t>Formuler et cadrer une demande</t>
         </is>
@@ -10062,12 +10126,12 @@
           <t>REF-120</t>
         </is>
       </c>
-      <c r="C141" s="24" t="inlineStr">
+      <c r="C141" s="23" t="inlineStr">
         <is>
           <t>11 – IA et assistance générative</t>
         </is>
       </c>
-      <c r="D141" s="24" t="inlineStr">
+      <c r="D141" s="23" t="inlineStr">
         <is>
           <t>Composants scriptés assistés</t>
         </is>
@@ -10127,12 +10191,12 @@
           <t>REF-121</t>
         </is>
       </c>
-      <c r="C142" s="24" t="inlineStr">
+      <c r="C142" s="23" t="inlineStr">
         <is>
           <t>11 – IA et assistance générative</t>
         </is>
       </c>
-      <c r="D142" s="24" t="inlineStr">
+      <c r="D142" s="23" t="inlineStr">
         <is>
           <t>Composants scriptés assistés</t>
         </is>
@@ -10192,12 +10256,12 @@
           <t>REF-122</t>
         </is>
       </c>
-      <c r="C143" s="24" t="inlineStr">
+      <c r="C143" s="23" t="inlineStr">
         <is>
           <t>11 – IA et assistance générative</t>
         </is>
       </c>
-      <c r="D143" s="24" t="inlineStr">
+      <c r="D143" s="23" t="inlineStr">
         <is>
           <t>Composants scriptés assistés</t>
         </is>
@@ -10257,12 +10321,12 @@
           <t>REF-123</t>
         </is>
       </c>
-      <c r="C144" s="24" t="inlineStr">
+      <c r="C144" s="23" t="inlineStr">
         <is>
           <t>11 – IA et assistance générative</t>
         </is>
       </c>
-      <c r="D144" s="24" t="inlineStr">
+      <c r="D144" s="23" t="inlineStr">
         <is>
           <t>Composants scriptés assistés</t>
         </is>
@@ -10322,12 +10386,12 @@
           <t>REF-124</t>
         </is>
       </c>
-      <c r="C145" s="24" t="inlineStr">
+      <c r="C145" s="23" t="inlineStr">
         <is>
           <t>11 – IA et assistance générative</t>
         </is>
       </c>
-      <c r="D145" s="24" t="inlineStr">
+      <c r="D145" s="23" t="inlineStr">
         <is>
           <t>Composants scriptés assistés</t>
         </is>
@@ -10387,12 +10451,12 @@
           <t>REF-125</t>
         </is>
       </c>
-      <c r="C146" s="24" t="inlineStr">
+      <c r="C146" s="23" t="inlineStr">
         <is>
           <t>11 – IA et assistance générative</t>
         </is>
       </c>
-      <c r="D146" s="24" t="inlineStr">
+      <c r="D146" s="23" t="inlineStr">
         <is>
           <t>Développement de plugins assisté</t>
         </is>
@@ -10452,12 +10516,12 @@
           <t>REF-126</t>
         </is>
       </c>
-      <c r="C147" s="24" t="inlineStr">
+      <c r="C147" s="23" t="inlineStr">
         <is>
           <t>11 – IA et assistance générative</t>
         </is>
       </c>
-      <c r="D147" s="24" t="inlineStr">
+      <c r="D147" s="23" t="inlineStr">
         <is>
           <t>Développement de plugins assisté</t>
         </is>
@@ -10517,12 +10581,12 @@
           <t>REF-127</t>
         </is>
       </c>
-      <c r="C148" s="24" t="inlineStr">
+      <c r="C148" s="23" t="inlineStr">
         <is>
           <t>11 – IA et assistance générative</t>
         </is>
       </c>
-      <c r="D148" s="24" t="inlineStr">
+      <c r="D148" s="23" t="inlineStr">
         <is>
           <t>Développement de plugins assisté</t>
         </is>
@@ -10582,12 +10646,12 @@
           <t>REF-128</t>
         </is>
       </c>
-      <c r="C149" s="24" t="inlineStr">
+      <c r="C149" s="23" t="inlineStr">
         <is>
           <t>11 – IA et assistance générative</t>
         </is>
       </c>
-      <c r="D149" s="24" t="inlineStr">
+      <c r="D149" s="23" t="inlineStr">
         <is>
           <t>Développement de plugins assisté</t>
         </is>
@@ -10647,12 +10711,12 @@
           <t>REF-129</t>
         </is>
       </c>
-      <c r="C150" s="24" t="inlineStr">
+      <c r="C150" s="23" t="inlineStr">
         <is>
           <t>11 – IA et assistance générative</t>
         </is>
       </c>
-      <c r="D150" s="24" t="inlineStr">
+      <c r="D150" s="23" t="inlineStr">
         <is>
           <t>Apprentissage automatique</t>
         </is>
@@ -10712,12 +10776,12 @@
           <t>REF-130</t>
         </is>
       </c>
-      <c r="C151" s="24" t="inlineStr">
+      <c r="C151" s="23" t="inlineStr">
         <is>
           <t>11 – IA et assistance générative</t>
         </is>
       </c>
-      <c r="D151" s="24" t="inlineStr">
+      <c r="D151" s="23" t="inlineStr">
         <is>
           <t>Apprentissage automatique</t>
         </is>
@@ -10777,12 +10841,12 @@
           <t>REF-131</t>
         </is>
       </c>
-      <c r="C152" s="24" t="inlineStr">
+      <c r="C152" s="23" t="inlineStr">
         <is>
           <t>11 – IA et assistance générative</t>
         </is>
       </c>
-      <c r="D152" s="24" t="inlineStr">
+      <c r="D152" s="23" t="inlineStr">
         <is>
           <t>Apprentissage automatique</t>
         </is>
@@ -10842,12 +10906,12 @@
           <t>REF-132</t>
         </is>
       </c>
-      <c r="C153" s="24" t="inlineStr">
+      <c r="C153" s="23" t="inlineStr">
         <is>
           <t>11 – IA et assistance générative</t>
         </is>
       </c>
-      <c r="D153" s="24" t="inlineStr">
+      <c r="D153" s="23" t="inlineStr">
         <is>
           <t>Apprentissage automatique</t>
         </is>
@@ -10907,12 +10971,12 @@
           <t>REF-133</t>
         </is>
       </c>
-      <c r="C154" s="24" t="inlineStr">
+      <c r="C154" s="23" t="inlineStr">
         <is>
           <t>11 – IA et assistance générative</t>
         </is>
       </c>
-      <c r="D154" s="24" t="inlineStr">
+      <c r="D154" s="23" t="inlineStr">
         <is>
           <t>Modèles de langage et IA générative</t>
         </is>
@@ -10972,12 +11036,12 @@
           <t>REF-134</t>
         </is>
       </c>
-      <c r="C155" s="24" t="inlineStr">
+      <c r="C155" s="23" t="inlineStr">
         <is>
           <t>11 – IA et assistance générative</t>
         </is>
       </c>
-      <c r="D155" s="24" t="inlineStr">
+      <c r="D155" s="23" t="inlineStr">
         <is>
           <t>Modèles de langage et IA générative</t>
         </is>
@@ -11037,12 +11101,12 @@
           <t>REF-135</t>
         </is>
       </c>
-      <c r="C156" s="24" t="inlineStr">
+      <c r="C156" s="23" t="inlineStr">
         <is>
           <t>11 – IA et assistance générative</t>
         </is>
       </c>
-      <c r="D156" s="24" t="inlineStr">
+      <c r="D156" s="23" t="inlineStr">
         <is>
           <t>Modèles de langage et IA générative</t>
         </is>
@@ -11102,12 +11166,12 @@
           <t>REF-136</t>
         </is>
       </c>
-      <c r="C157" s="24" t="inlineStr">
+      <c r="C157" s="23" t="inlineStr">
         <is>
           <t>11 – IA et assistance générative</t>
         </is>
       </c>
-      <c r="D157" s="24" t="inlineStr">
+      <c r="D157" s="23" t="inlineStr">
         <is>
           <t>Agents et protocoles</t>
         </is>
@@ -11167,12 +11231,12 @@
           <t>REF-137</t>
         </is>
       </c>
-      <c r="C158" s="24" t="inlineStr">
+      <c r="C158" s="23" t="inlineStr">
         <is>
           <t>11 – IA et assistance générative</t>
         </is>
       </c>
-      <c r="D158" s="24" t="inlineStr">
+      <c r="D158" s="23" t="inlineStr">
         <is>
           <t>Agents et protocoles</t>
         </is>
@@ -11232,12 +11296,12 @@
           <t>REF-138</t>
         </is>
       </c>
-      <c r="C159" s="24" t="inlineStr">
+      <c r="C159" s="23" t="inlineStr">
         <is>
           <t>11 – IA et assistance générative</t>
         </is>
       </c>
-      <c r="D159" s="24" t="inlineStr">
+      <c r="D159" s="23" t="inlineStr">
         <is>
           <t>Agents et protocoles</t>
         </is>
@@ -11297,12 +11361,12 @@
           <t>REF-139</t>
         </is>
       </c>
-      <c r="C160" s="24" t="inlineStr">
+      <c r="C160" s="23" t="inlineStr">
         <is>
           <t>11 – IA et assistance générative</t>
         </is>
       </c>
-      <c r="D160" s="24" t="inlineStr">
+      <c r="D160" s="23" t="inlineStr">
         <is>
           <t>Vérification, licences et limites</t>
         </is>
@@ -11362,12 +11426,12 @@
           <t>REF-140</t>
         </is>
       </c>
-      <c r="C161" s="24" t="inlineStr">
+      <c r="C161" s="23" t="inlineStr">
         <is>
           <t>11 – IA et assistance générative</t>
         </is>
       </c>
-      <c r="D161" s="24" t="inlineStr">
+      <c r="D161" s="23" t="inlineStr">
         <is>
           <t>Vérification, licences et limites</t>
         </is>
@@ -11427,12 +11491,12 @@
           <t>REF-141</t>
         </is>
       </c>
-      <c r="C162" s="24" t="inlineStr">
+      <c r="C162" s="23" t="inlineStr">
         <is>
           <t>11 – IA et assistance générative</t>
         </is>
       </c>
-      <c r="D162" s="24" t="inlineStr">
+      <c r="D162" s="23" t="inlineStr">
         <is>
           <t>Vérification, licences et limites</t>
         </is>
@@ -11492,12 +11556,12 @@
           <t>REF-142</t>
         </is>
       </c>
-      <c r="C163" s="24" t="inlineStr">
+      <c r="C163" s="23" t="inlineStr">
         <is>
           <t>11 – IA et assistance générative</t>
         </is>
       </c>
-      <c r="D163" s="24" t="inlineStr">
+      <c r="D163" s="23" t="inlineStr">
         <is>
           <t>Vérification, licences et limites</t>
         </is>
@@ -22995,363 +23059,363 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="25" t="inlineStr">
+      <c r="A3" s="24" t="inlineStr">
         <is>
           <t>Répartition par domaine</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="26" t="inlineStr">
+      <c r="A4" s="25" t="inlineStr">
         <is>
           <t>Domaine</t>
         </is>
       </c>
-      <c r="B4" s="26" t="inlineStr">
+      <c r="B4" s="25" t="inlineStr">
         <is>
           <t>Nb notions</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="27" t="inlineStr">
+      <c r="A5" s="26" t="inlineStr">
         <is>
           <t>1 – Socle Rhino (prérequis)</t>
         </is>
       </c>
-      <c r="B5" s="28">
+      <c r="B5" s="27">
         <f>COUNTIF(Référentiel!$C$4:$C$163,$A$5)</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="27" t="inlineStr">
+      <c r="A6" s="26" t="inlineStr">
         <is>
           <t>10 – Aide à la fabrication</t>
         </is>
       </c>
-      <c r="B6" s="28">
+      <c r="B6" s="27">
         <f>COUNTIF(Référentiel!$C$4:$C$163,$A$6)</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="27" t="inlineStr">
+      <c r="A7" s="26" t="inlineStr">
         <is>
           <t>11 – IA et assistance générative</t>
         </is>
       </c>
-      <c r="B7" s="28">
+      <c r="B7" s="27">
         <f>COUNTIF(Référentiel!$C$4:$C$163,$A$7)</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="27" t="inlineStr">
+      <c r="A8" s="26" t="inlineStr">
         <is>
           <t>2 – Environnement et principes Grasshopper</t>
         </is>
       </c>
-      <c r="B8" s="28">
+      <c r="B8" s="27">
         <f>COUNTIF(Référentiel!$C$4:$C$163,$A$8)</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="27" t="inlineStr">
+      <c r="A9" s="26" t="inlineStr">
         <is>
           <t>3 – Données et logique</t>
         </is>
       </c>
-      <c r="B9" s="28">
+      <c r="B9" s="27">
         <f>COUNTIF(Référentiel!$C$4:$C$163,$A$9)</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="27" t="inlineStr">
+      <c r="A10" s="26" t="inlineStr">
         <is>
           <t>4 – Géométrie paramétrique</t>
         </is>
       </c>
-      <c r="B10" s="28">
+      <c r="B10" s="27">
         <f>COUNTIF(Référentiel!$C$4:$C$163,$A$10)</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="27" t="inlineStr">
+      <c r="A11" s="26" t="inlineStr">
         <is>
           <t>5 – Mesures, quantitatifs et export</t>
         </is>
       </c>
-      <c r="B11" s="28">
+      <c r="B11" s="27">
         <f>COUNTIF(Référentiel!$C$4:$C$163,$A$11)</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="27" t="inlineStr">
+      <c r="A12" s="26" t="inlineStr">
         <is>
           <t>6 – Méthode, performance et évènements</t>
         </is>
       </c>
-      <c r="B12" s="28">
+      <c r="B12" s="27">
         <f>COUNTIF(Référentiel!$C$4:$C$163,$A$12)</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="27" t="inlineStr">
+      <c r="A13" s="26" t="inlineStr">
         <is>
           <t>7 – Algorithmique avancée</t>
         </is>
       </c>
-      <c r="B13" s="28">
+      <c r="B13" s="27">
         <f>COUNTIF(Référentiel!$C$4:$C$163,$A$13)</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="27" t="inlineStr">
+      <c r="A14" s="26" t="inlineStr">
         <is>
           <t>8 – Développement, scripting et API</t>
         </is>
       </c>
-      <c r="B14" s="28">
+      <c r="B14" s="27">
         <f>COUNTIF(Référentiel!$C$4:$C$163,$A$14)</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="27" t="inlineStr">
+      <c r="A15" s="26" t="inlineStr">
         <is>
           <t>9 – Interfaces, web et interopérabilité</t>
         </is>
       </c>
-      <c r="B15" s="28">
+      <c r="B15" s="27">
         <f>COUNTIF(Référentiel!$C$4:$C$163,$A$15)</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="25" t="inlineStr">
+      <c r="A17" s="24" t="inlineStr">
         <is>
           <t>Répartition par niveau</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="26" t="inlineStr">
+      <c r="A18" s="25" t="inlineStr">
         <is>
           <t>Niveau</t>
         </is>
       </c>
-      <c r="B18" s="26" t="inlineStr">
+      <c r="B18" s="25" t="inlineStr">
         <is>
           <t>Nb notions</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="27" t="inlineStr">
+      <c r="A19" s="26" t="inlineStr">
         <is>
           <t>Débutant</t>
         </is>
       </c>
-      <c r="B19" s="28">
+      <c r="B19" s="27">
         <f>COUNTIF(Référentiel!$G$4:$G$163,$A$19)</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="27" t="inlineStr">
+      <c r="A20" s="26" t="inlineStr">
         <is>
           <t>Intermédiaire</t>
         </is>
       </c>
-      <c r="B20" s="28">
+      <c r="B20" s="27">
         <f>COUNTIF(Référentiel!$G$4:$G$163,$A$20)</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="27" t="inlineStr">
+      <c r="A21" s="26" t="inlineStr">
         <is>
           <t>Perfectionnement</t>
         </is>
       </c>
-      <c r="B21" s="28">
+      <c r="B21" s="27">
         <f>COUNTIF(Référentiel!$G$4:$G$163,$A$21)</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="27" t="inlineStr">
+      <c r="A22" s="26" t="inlineStr">
         <is>
           <t>Expert</t>
         </is>
       </c>
-      <c r="B22" s="28">
+      <c r="B22" s="27">
         <f>COUNTIF(Référentiel!$G$4:$G$163,$A$22)</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="25" t="inlineStr">
+      <c r="A24" s="24" t="inlineStr">
         <is>
           <t>Répartition par mode de validation</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="26" t="inlineStr">
+      <c r="A25" s="25" t="inlineStr">
         <is>
           <t>Mode de validation</t>
         </is>
       </c>
-      <c r="B25" s="26" t="inlineStr">
+      <c r="B25" s="25" t="inlineStr">
         <is>
           <t>Nb notions</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="27" t="inlineStr">
+      <c r="A26" s="26" t="inlineStr">
         <is>
           <t>ExactOrderedList</t>
         </is>
       </c>
-      <c r="B26" s="28">
+      <c r="B26" s="27">
         <f>COUNTIF(Référentiel!$H$4:$H$163,$A$26)</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="27" t="inlineStr">
+      <c r="A27" s="26" t="inlineStr">
         <is>
           <t>SetEquality</t>
         </is>
       </c>
-      <c r="B27" s="28">
+      <c r="B27" s="27">
         <f>COUNTIF(Référentiel!$H$4:$H$163,$A$27)</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="27" t="inlineStr">
+      <c r="A28" s="26" t="inlineStr">
         <is>
           <t>SingleValue</t>
         </is>
       </c>
-      <c r="B28" s="28">
+      <c r="B28" s="27">
         <f>COUNTIF(Référentiel!$H$4:$H$163,$A$28)</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="27" t="inlineStr">
+      <c r="A29" s="26" t="inlineStr">
         <is>
           <t>NumericTolerance</t>
         </is>
       </c>
-      <c r="B29" s="28">
+      <c r="B29" s="27">
         <f>COUNTIF(Référentiel!$H$4:$H$163,$A$29)</f>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="27" t="inlineStr">
+      <c r="A30" s="26" t="inlineStr">
         <is>
           <t>GeometryTolerance</t>
         </is>
       </c>
-      <c r="B30" s="28">
+      <c r="B30" s="27">
         <f>COUNTIF(Référentiel!$H$4:$H$163,$A$30)</f>
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="27" t="inlineStr">
+      <c r="A31" s="26" t="inlineStr">
         <is>
           <t>Conceptuel (QCM)</t>
         </is>
       </c>
-      <c r="B31" s="28">
+      <c r="B31" s="27">
         <f>COUNTIF(Référentiel!$H$4:$H$163,$A$31)</f>
         <v/>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="25" t="inlineStr">
+      <c r="A33" s="24" t="inlineStr">
         <is>
           <t>Répartition par type d'exercice</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="26" t="inlineStr">
+      <c r="A34" s="25" t="inlineStr">
         <is>
           <t>Type d'exercice</t>
         </is>
       </c>
-      <c r="B34" s="26" t="inlineStr">
+      <c r="B34" s="25" t="inlineStr">
         <is>
           <t>Nb notions</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="27" t="inlineStr">
+      <c r="A35" s="26" t="inlineStr">
         <is>
           <t>Exercice Grasshopper</t>
         </is>
       </c>
-      <c r="B35" s="28">
+      <c r="B35" s="27">
         <f>COUNTIF(Référentiel!$I$4:$I$163,$A$35)</f>
         <v/>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="27" t="inlineStr">
+      <c r="A36" s="26" t="inlineStr">
         <is>
           <t>Exercice de synthèse</t>
         </is>
       </c>
-      <c r="B36" s="28">
+      <c r="B36" s="27">
         <f>COUNTIF(Référentiel!$I$4:$I$163,$A$36)</f>
         <v/>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="27" t="inlineStr">
+      <c r="A37" s="26" t="inlineStr">
         <is>
           <t>QCM / question ciblée</t>
         </is>
       </c>
-      <c r="B37" s="28">
+      <c r="B37" s="27">
         <f>COUNTIF(Référentiel!$I$4:$I$163,$A$37)</f>
         <v/>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="27" t="inlineStr">
+      <c r="A38" s="26" t="inlineStr">
         <is>
           <t>Démonstration formateur</t>
         </is>
       </c>
-      <c r="B38" s="28">
+      <c r="B38" s="27">
         <f>COUNTIF(Référentiel!$I$4:$I$163,$A$38)</f>
         <v/>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="29" t="inlineStr">
+      <c r="A40" s="28" t="inlineStr">
         <is>
           <t>Total des notions</t>
         </is>
       </c>
-      <c r="B40" s="29" t="n">
+      <c r="B40" s="28" t="n">
         <v>160</v>
       </c>
     </row>
@@ -23390,207 +23454,207 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="30" t="inlineStr">
+      <c r="A3" s="29" t="inlineStr">
         <is>
           <t>Domaines</t>
         </is>
       </c>
-      <c r="B3" s="30" t="inlineStr">
+      <c r="B3" s="29" t="inlineStr">
         <is>
           <t>Niveaux</t>
         </is>
       </c>
-      <c r="C3" s="30" t="inlineStr">
+      <c r="C3" s="29" t="inlineStr">
         <is>
           <t>ValidationMode</t>
         </is>
       </c>
-      <c r="D3" s="30" t="inlineStr">
+      <c r="D3" s="29" t="inlineStr">
         <is>
           <t>Types d'exercice</t>
         </is>
       </c>
-      <c r="E3" s="30" t="inlineStr">
+      <c r="E3" s="29" t="inlineStr">
         <is>
           <t>Priorités</t>
         </is>
       </c>
-      <c r="F3" s="30" t="inlineStr">
+      <c r="F3" s="29" t="inlineStr">
         <is>
           <t>Statuts</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="27" t="inlineStr">
+      <c r="A4" s="26" t="inlineStr">
         <is>
           <t>0 – Socle Rhino (prérequis)</t>
         </is>
       </c>
-      <c r="B4" s="27" t="inlineStr">
+      <c r="B4" s="26" t="inlineStr">
         <is>
           <t>Débutant</t>
         </is>
       </c>
-      <c r="C4" s="27" t="inlineStr">
+      <c r="C4" s="26" t="inlineStr">
         <is>
           <t>ExactOrderedList</t>
         </is>
       </c>
-      <c r="D4" s="27" t="inlineStr">
+      <c r="D4" s="26" t="inlineStr">
         <is>
           <t>Exercice Grasshopper</t>
         </is>
       </c>
-      <c r="E4" s="27" t="inlineStr">
+      <c r="E4" s="26" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="F4" s="27" t="inlineStr">
+      <c r="F4" s="26" t="inlineStr">
         <is>
           <t>Pas commencé</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="27" t="inlineStr">
+      <c r="A5" s="26" t="inlineStr">
         <is>
           <t>1 – Environnement et principes Grasshopper</t>
         </is>
       </c>
-      <c r="B5" s="27" t="inlineStr">
+      <c r="B5" s="26" t="inlineStr">
         <is>
           <t>Intermédiaire</t>
         </is>
       </c>
-      <c r="C5" s="27" t="inlineStr">
+      <c r="C5" s="26" t="inlineStr">
         <is>
           <t>SetEquality</t>
         </is>
       </c>
-      <c r="D5" s="27" t="inlineStr">
+      <c r="D5" s="26" t="inlineStr">
         <is>
           <t>Exercice de synthèse</t>
         </is>
       </c>
-      <c r="E5" s="27" t="inlineStr">
+      <c r="E5" s="26" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="F5" s="27" t="inlineStr">
+      <c r="F5" s="26" t="inlineStr">
         <is>
           <t>En cours</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="27" t="inlineStr">
+      <c r="A6" s="26" t="inlineStr">
         <is>
           <t>2 – Données et logique</t>
         </is>
       </c>
-      <c r="B6" s="27" t="inlineStr">
+      <c r="B6" s="26" t="inlineStr">
         <is>
           <t>Perfectionnement</t>
         </is>
       </c>
-      <c r="C6" s="27" t="inlineStr">
+      <c r="C6" s="26" t="inlineStr">
         <is>
           <t>SingleValue</t>
         </is>
       </c>
-      <c r="D6" s="27" t="inlineStr">
+      <c r="D6" s="26" t="inlineStr">
         <is>
           <t>QCM / question ciblée</t>
         </is>
       </c>
-      <c r="E6" s="27" t="inlineStr">
+      <c r="E6" s="26" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="F6" s="27" t="inlineStr">
+      <c r="F6" s="26" t="inlineStr">
         <is>
           <t>Terminé</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="27" t="inlineStr">
+      <c r="A7" s="26" t="inlineStr">
         <is>
           <t>3 – Géométrie paramétrique</t>
         </is>
       </c>
-      <c r="B7" s="27" t="inlineStr">
+      <c r="B7" s="26" t="inlineStr">
         <is>
           <t>Expert</t>
         </is>
       </c>
-      <c r="C7" s="27" t="inlineStr">
+      <c r="C7" s="26" t="inlineStr">
         <is>
           <t>NumericTolerance</t>
         </is>
       </c>
-      <c r="D7" s="27" t="inlineStr">
+      <c r="D7" s="26" t="inlineStr">
         <is>
           <t>Démonstration formateur</t>
         </is>
       </c>
-      <c r="F7" s="27" t="inlineStr">
+      <c r="F7" s="26" t="inlineStr">
         <is>
           <t>Bloqué</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="27" t="inlineStr">
+      <c r="A8" s="26" t="inlineStr">
         <is>
           <t>4 – Mesures, quantitatifs et export</t>
         </is>
       </c>
-      <c r="C8" s="27" t="inlineStr">
+      <c r="C8" s="26" t="inlineStr">
         <is>
           <t>GeometryTolerance</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="27" t="inlineStr">
+      <c r="A9" s="26" t="inlineStr">
         <is>
           <t>5 – Méthode, performance et évènements</t>
         </is>
       </c>
-      <c r="C9" s="27" t="inlineStr">
+      <c r="C9" s="26" t="inlineStr">
         <is>
           <t>Conceptuel (QCM)</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="27" t="inlineStr">
+      <c r="A10" s="26" t="inlineStr">
         <is>
           <t>6 – Algorithmique avancée</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="27" t="inlineStr">
+      <c r="A11" s="26" t="inlineStr">
         <is>
           <t>7 – Développement, scripting et API</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="27" t="inlineStr">
+      <c r="A12" s="26" t="inlineStr">
         <is>
           <t>8 – Interfaces, web et interopérabilité</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="27" t="inlineStr">
+      <c r="A13" s="26" t="inlineStr">
         <is>
           <t>9 – Aide à la fabrication</t>
         </is>

--- a/Fondamentaux Grasshopper - IndC - 01-09-2026.xlsx
+++ b/Fondamentaux Grasshopper - IndC - 01-09-2026.xlsx
@@ -2959,7 +2959,7 @@
       </c>
       <c r="Q30" s="10" t="inlineStr">
         <is>
-          <t>A-04</t>
+          <t>A-04, G-26</t>
         </is>
       </c>
     </row>
@@ -3024,7 +3024,7 @@
       </c>
       <c r="Q31" s="10" t="inlineStr">
         <is>
-          <t>A-01, A-03, A-05, C-01</t>
+          <t>A-01, A-03, A-05, C-01, G-14, G-24</t>
         </is>
       </c>
     </row>
@@ -3089,7 +3089,7 @@
       </c>
       <c r="Q32" s="10" t="inlineStr">
         <is>
-          <t>A-01, A-05</t>
+          <t>A-01, A-05, G-09, G-19</t>
         </is>
       </c>
     </row>
@@ -3869,7 +3869,7 @@
       </c>
       <c r="Q44" s="10" t="inlineStr">
         <is>
-          <t>A-06, A-08</t>
+          <t>A-06, A-08, G-17, G-18</t>
         </is>
       </c>
     </row>
@@ -3927,14 +3927,14 @@
       <c r="M45" s="7" t="inlineStr"/>
       <c r="N45" s="8" t="inlineStr"/>
       <c r="O45" s="10" t="inlineStr"/>
-      <c r="P45" s="12" t="inlineStr">
-        <is>
-          <t>Connaissance</t>
+      <c r="P45" s="11" t="inlineStr">
+        <is>
+          <t>Compétence</t>
         </is>
       </c>
       <c r="Q45" s="10" t="inlineStr">
         <is>
-          <t>A-07</t>
+          <t>A-07, G-18, G-20</t>
         </is>
       </c>
     </row>
@@ -4064,7 +4064,7 @@
       </c>
       <c r="Q47" s="10" t="inlineStr">
         <is>
-          <t>A-11, A-17, A-18</t>
+          <t>A-11, A-17, A-18, G-03, G-19</t>
         </is>
       </c>
     </row>
@@ -4129,7 +4129,7 @@
       </c>
       <c r="Q48" s="10" t="inlineStr">
         <is>
-          <t>A-10, A-12, A-18, B-01, B-02, B-08</t>
+          <t>A-10, A-12, A-18, B-01, B-02, B-08, G-01, G-03, G-21</t>
         </is>
       </c>
     </row>
@@ -4194,7 +4194,7 @@
       </c>
       <c r="Q49" s="10" t="inlineStr">
         <is>
-          <t>A-13, B-08, B-15</t>
+          <t>A-13, B-08, B-15, G-08, G-23</t>
         </is>
       </c>
     </row>
@@ -4259,7 +4259,7 @@
       </c>
       <c r="Q50" s="10" t="inlineStr">
         <is>
-          <t>A-14, A-15, B-13, B-15, C-09</t>
+          <t>A-14, A-15, B-13, B-15, C-09, G-08, G-10, G-13</t>
         </is>
       </c>
     </row>
@@ -4324,7 +4324,7 @@
       </c>
       <c r="Q51" s="10" t="inlineStr">
         <is>
-          <t>A-16, B-05, B-11, C-03</t>
+          <t>A-16, B-05, B-11, C-03, G-08, G-21</t>
         </is>
       </c>
     </row>
@@ -4389,7 +4389,7 @@
       </c>
       <c r="Q52" s="10" t="inlineStr">
         <is>
-          <t>A-10, A-13, B-01, B-02, B-08, C-03</t>
+          <t>A-10, A-13, B-01, B-02, B-08, C-03, G-01, G-12, G-22, G-29</t>
         </is>
       </c>
     </row>
@@ -4454,7 +4454,7 @@
       </c>
       <c r="Q53" s="10" t="inlineStr">
         <is>
-          <t>A-19, A-22</t>
+          <t>A-19, A-22, G-14, G-30, G-31</t>
         </is>
       </c>
     </row>
@@ -4519,7 +4519,7 @@
       </c>
       <c r="Q54" s="10" t="inlineStr">
         <is>
-          <t>A-20, B-04, B-10, B-17, C-02</t>
+          <t>A-20, B-04, B-10, B-17, C-02, G-12, G-32</t>
         </is>
       </c>
     </row>
@@ -4584,7 +4584,7 @@
       </c>
       <c r="Q55" s="10" t="inlineStr">
         <is>
-          <t>A-21, A-23</t>
+          <t>A-21, A-23, G-32</t>
         </is>
       </c>
     </row>
@@ -4649,7 +4649,7 @@
       </c>
       <c r="Q56" s="10" t="inlineStr">
         <is>
-          <t>A-19, A-22</t>
+          <t>A-19, A-22, G-12, G-22, G-31</t>
         </is>
       </c>
     </row>
@@ -4714,7 +4714,7 @@
       </c>
       <c r="Q57" s="10" t="inlineStr">
         <is>
-          <t>A-20</t>
+          <t>A-20, G-32</t>
         </is>
       </c>
     </row>
@@ -4783,7 +4783,7 @@
       </c>
       <c r="Q58" s="10" t="inlineStr">
         <is>
-          <t>A-24, B-03</t>
+          <t>A-24, B-03, G-04, G-17, G-20</t>
         </is>
       </c>
     </row>
@@ -4848,7 +4848,7 @@
       </c>
       <c r="Q59" s="10" t="inlineStr">
         <is>
-          <t>A-25, B-03</t>
+          <t>A-25, B-03, G-04</t>
         </is>
       </c>
     </row>
@@ -4913,7 +4913,7 @@
       </c>
       <c r="Q60" s="10" t="inlineStr">
         <is>
-          <t>A-09</t>
+          <t>A-09, G-16, G-20</t>
         </is>
       </c>
     </row>
@@ -4971,14 +4971,14 @@
       <c r="M61" s="7" t="inlineStr"/>
       <c r="N61" s="8" t="inlineStr"/>
       <c r="O61" s="10" t="inlineStr"/>
-      <c r="P61" s="12" t="inlineStr">
-        <is>
-          <t>Connaissance</t>
+      <c r="P61" s="11" t="inlineStr">
+        <is>
+          <t>Compétence</t>
         </is>
       </c>
       <c r="Q61" s="10" t="inlineStr">
         <is>
-          <t>A-26</t>
+          <t>A-26, G-09, G-17</t>
         </is>
       </c>
     </row>
@@ -5043,7 +5043,7 @@
       </c>
       <c r="Q62" s="10" t="inlineStr">
         <is>
-          <t>A-27, B-14</t>
+          <t>A-27, B-14, G-11</t>
         </is>
       </c>
     </row>
@@ -5108,7 +5108,7 @@
       </c>
       <c r="Q63" s="10" t="inlineStr">
         <is>
-          <t>A-28</t>
+          <t>A-28, G-11</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="Q65" s="10" t="inlineStr">
         <is>
-          <t>A-08, A-29</t>
+          <t>A-08, A-29, G-06, G-18, G-26</t>
         </is>
       </c>
     </row>
@@ -5303,7 +5303,7 @@
       </c>
       <c r="Q66" s="10" t="inlineStr">
         <is>
-          <t>A-30, C-03</t>
+          <t>A-30, C-03, G-06</t>
         </is>
       </c>
     </row>
@@ -5368,7 +5368,7 @@
       </c>
       <c r="Q67" s="10" t="inlineStr">
         <is>
-          <t>A-15, A-31</t>
+          <t>A-15, A-31, G-06, G-24, G-28</t>
         </is>
       </c>
     </row>
@@ -5433,7 +5433,7 @@
       </c>
       <c r="Q68" s="10" t="inlineStr">
         <is>
-          <t>A-02, A-32, A-33</t>
+          <t>A-02, A-32, A-33, G-02</t>
         </is>
       </c>
     </row>
@@ -5498,7 +5498,7 @@
       </c>
       <c r="Q69" s="10" t="inlineStr">
         <is>
-          <t>A-34, A-36, B-05</t>
+          <t>A-34, A-36, B-05, G-02, G-15, G-27</t>
         </is>
       </c>
     </row>
@@ -5823,7 +5823,7 @@
       </c>
       <c r="Q74" s="10" t="inlineStr">
         <is>
-          <t>A-37, A-38, A-40, B-01, B-09, B-11, B-16</t>
+          <t>A-37, A-38, A-40, B-01, B-09, B-11, B-16, G-07, G-15, G-25, G-27, G-28</t>
         </is>
       </c>
     </row>
@@ -5888,7 +5888,7 @@
       </c>
       <c r="Q75" s="10" t="inlineStr">
         <is>
-          <t>A-39, B-01, B-03, B-04, B-06, B-09, C-01, C-08, C-09</t>
+          <t>A-39, B-01, B-03, B-04, B-06, B-09, C-01, C-08, C-09, G-07, G-10, G-13, G-21, G-22, G-27</t>
         </is>
       </c>
     </row>
@@ -6798,7 +6798,7 @@
       </c>
       <c r="Q89" s="10" t="inlineStr">
         <is>
-          <t>A-47, B-05, C-01, C-03, C-08</t>
+          <t>A-47, B-05, C-01, C-03, C-08, G-05, G-22, G-29</t>
         </is>
       </c>
     </row>
@@ -6928,7 +6928,7 @@
       </c>
       <c r="Q91" s="10" t="inlineStr">
         <is>
-          <t>A-49, B-14, C-08</t>
+          <t>A-49, B-14, C-08, G-05</t>
         </is>
       </c>
     </row>
@@ -6993,7 +6993,7 @@
       </c>
       <c r="Q92" s="10" t="inlineStr">
         <is>
-          <t>B-12, B-13, B-15, C-04, C-05, C-07, C-11, QT-01</t>
+          <t>B-12, B-13, B-15, C-04, C-05, C-07, C-11, G-23, QT-01</t>
         </is>
       </c>
     </row>
@@ -7383,7 +7383,7 @@
       </c>
       <c r="Q98" s="10" t="inlineStr">
         <is>
-          <t>MP-01</t>
+          <t>G-30, MP-01</t>
         </is>
       </c>
     </row>
@@ -7578,7 +7578,7 @@
       </c>
       <c r="Q101" s="10" t="inlineStr">
         <is>
-          <t>A-26, MP-04</t>
+          <t>A-26, G-25, MP-04</t>
         </is>
       </c>
     </row>
@@ -7773,7 +7773,7 @@
       </c>
       <c r="Q104" s="10" t="inlineStr">
         <is>
-          <t>AV-01</t>
+          <t>AV-01, G-25</t>
         </is>
       </c>
     </row>
@@ -8488,7 +8488,7 @@
       </c>
       <c r="Q115" s="10" t="inlineStr">
         <is>
-          <t>DV-04, DV-07</t>
+          <t>DV-04, DV-07, G-05</t>
         </is>
       </c>
     </row>
@@ -8683,7 +8683,7 @@
       </c>
       <c r="Q118" s="10" t="inlineStr">
         <is>
-          <t>B-17, C-09, DV-02</t>
+          <t>B-17, C-09, DV-02, G-16</t>
         </is>
       </c>
     </row>
@@ -9008,7 +9008,7 @@
       </c>
       <c r="Q123" s="10" t="inlineStr">
         <is>
-          <t>C-07, WB-01</t>
+          <t>C-07, G-28, WB-01</t>
         </is>
       </c>
     </row>

--- a/Fondamentaux Grasshopper - IndC - 01-09-2026.xlsx
+++ b/Fondamentaux Grasshopper - IndC - 01-09-2026.xlsx
@@ -210,11 +210,11 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -1399,7 +1399,7 @@
       </c>
       <c r="Q6" s="10" t="inlineStr">
         <is>
-          <t>RH-01, RH-11</t>
+          <t>RH-01, RH-11, RH-30</t>
         </is>
       </c>
     </row>
@@ -1464,7 +1464,7 @@
       </c>
       <c r="Q7" s="10" t="inlineStr">
         <is>
-          <t>RH-02, RH-13</t>
+          <t>RH-02, RH-13, RH-30</t>
         </is>
       </c>
     </row>
@@ -1522,14 +1522,14 @@
       <c r="M8" s="7" t="inlineStr"/>
       <c r="N8" s="8" t="inlineStr"/>
       <c r="O8" s="10" t="inlineStr"/>
-      <c r="P8" s="12" t="inlineStr">
-        <is>
-          <t>Connaissance</t>
+      <c r="P8" s="11" t="inlineStr">
+        <is>
+          <t>Compétence</t>
         </is>
       </c>
       <c r="Q8" s="10" t="inlineStr">
         <is>
-          <t>RH-06</t>
+          <t>RH-06, RH-31</t>
         </is>
       </c>
     </row>
@@ -1594,7 +1594,7 @@
       </c>
       <c r="Q9" s="10" t="inlineStr">
         <is>
-          <t>RH-02, RH-13</t>
+          <t>RH-02, RH-13, RH-31</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="Q10" s="10" t="inlineStr">
         <is>
-          <t>RH-03</t>
+          <t>RH-03, RH-27</t>
         </is>
       </c>
     </row>
@@ -1724,7 +1724,7 @@
       </c>
       <c r="Q11" s="10" t="inlineStr">
         <is>
-          <t>RH-03, RH-14</t>
+          <t>RH-03, RH-14, RH-27</t>
         </is>
       </c>
     </row>
@@ -1789,7 +1789,7 @@
       </c>
       <c r="Q12" s="10" t="inlineStr">
         <is>
-          <t>RH-04, RH-15</t>
+          <t>RH-04, RH-15, RH-28</t>
         </is>
       </c>
     </row>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="Q13" s="10" t="inlineStr">
         <is>
-          <t>RH-04, RH-16</t>
+          <t>RH-04, RH-16, RH-28</t>
         </is>
       </c>
     </row>
@@ -1919,7 +1919,7 @@
       </c>
       <c r="Q14" s="10" t="inlineStr">
         <is>
-          <t>RH-04, RH-16</t>
+          <t>RH-04, RH-16, RH-28</t>
         </is>
       </c>
     </row>
@@ -1984,7 +1984,7 @@
       </c>
       <c r="Q15" s="10" t="inlineStr">
         <is>
-          <t>RH-05, RH-17</t>
+          <t>RH-05, RH-17, RH-29</t>
         </is>
       </c>
     </row>
@@ -2049,7 +2049,7 @@
       </c>
       <c r="Q16" s="10" t="inlineStr">
         <is>
-          <t>RH-03, RH-14</t>
+          <t>RH-03, RH-14, RH-29</t>
         </is>
       </c>
     </row>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="Q17" s="10" t="inlineStr">
         <is>
-          <t>RH-02</t>
+          <t>RH-02, RH-32</t>
         </is>
       </c>
     </row>
@@ -2172,14 +2172,14 @@
       <c r="M18" s="7" t="inlineStr"/>
       <c r="N18" s="8" t="inlineStr"/>
       <c r="O18" s="10" t="inlineStr"/>
-      <c r="P18" s="12" t="inlineStr">
-        <is>
-          <t>Connaissance</t>
+      <c r="P18" s="11" t="inlineStr">
+        <is>
+          <t>Compétence</t>
         </is>
       </c>
       <c r="Q18" s="10" t="inlineStr">
         <is>
-          <t>RH-07</t>
+          <t>RH-07, RH-32</t>
         </is>
       </c>
     </row>
@@ -2244,7 +2244,7 @@
       </c>
       <c r="Q19" s="10" t="inlineStr">
         <is>
-          <t>RH-23</t>
+          <t>RH-23, RH-32</t>
         </is>
       </c>
     </row>
@@ -2309,7 +2309,7 @@
       </c>
       <c r="Q20" s="10" t="inlineStr">
         <is>
-          <t>RH-09, RH-18</t>
+          <t>RH-09, RH-18, RH-24</t>
         </is>
       </c>
     </row>
@@ -2374,7 +2374,7 @@
       </c>
       <c r="Q21" s="10" t="inlineStr">
         <is>
-          <t>RH-07, RH-19</t>
+          <t>RH-07, RH-19, RH-24</t>
         </is>
       </c>
     </row>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="Q22" s="10" t="inlineStr">
         <is>
-          <t>RH-09, RH-19</t>
+          <t>RH-09, RH-19, RH-24</t>
         </is>
       </c>
     </row>
@@ -2504,7 +2504,7 @@
       </c>
       <c r="Q23" s="10" t="inlineStr">
         <is>
-          <t>RH-08, RH-20</t>
+          <t>RH-08, RH-20, RH-25</t>
         </is>
       </c>
     </row>
@@ -2569,7 +2569,7 @@
       </c>
       <c r="Q24" s="10" t="inlineStr">
         <is>
-          <t>RH-08, RH-20</t>
+          <t>RH-08, RH-20, RH-25</t>
         </is>
       </c>
     </row>
@@ -2634,7 +2634,7 @@
       </c>
       <c r="Q25" s="10" t="inlineStr">
         <is>
-          <t>RH-08, RH-20</t>
+          <t>RH-08, RH-20, RH-25</t>
         </is>
       </c>
     </row>
@@ -2699,7 +2699,7 @@
       </c>
       <c r="Q26" s="10" t="inlineStr">
         <is>
-          <t>RH-08, RH-21</t>
+          <t>RH-08, RH-21, RH-26</t>
         </is>
       </c>
     </row>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="Q27" s="10" t="inlineStr">
         <is>
-          <t>RH-08, RH-21</t>
+          <t>RH-08, RH-21, RH-26</t>
         </is>
       </c>
     </row>
@@ -2829,7 +2829,7 @@
       </c>
       <c r="Q28" s="10" t="inlineStr">
         <is>
-          <t>RH-10, RH-22</t>
+          <t>RH-10, RH-22, RH-26</t>
         </is>
       </c>
     </row>
@@ -2842,12 +2842,12 @@
           <t>REF-025</t>
         </is>
       </c>
-      <c r="C29" s="13" t="inlineStr">
+      <c r="C29" s="12" t="inlineStr">
         <is>
           <t>2 – Environnement et principes Grasshopper</t>
         </is>
       </c>
-      <c r="D29" s="13" t="inlineStr">
+      <c r="D29" s="12" t="inlineStr">
         <is>
           <t>Principes et interface Grasshopper</t>
         </is>
@@ -2887,7 +2887,7 @@
       <c r="M29" s="7" t="inlineStr"/>
       <c r="N29" s="8" t="inlineStr"/>
       <c r="O29" s="10" t="inlineStr"/>
-      <c r="P29" s="12" t="inlineStr">
+      <c r="P29" s="13" t="inlineStr">
         <is>
           <t>Connaissance</t>
         </is>
@@ -2907,12 +2907,12 @@
           <t>REF-026</t>
         </is>
       </c>
-      <c r="C30" s="13" t="inlineStr">
+      <c r="C30" s="12" t="inlineStr">
         <is>
           <t>2 – Environnement et principes Grasshopper</t>
         </is>
       </c>
-      <c r="D30" s="13" t="inlineStr">
+      <c r="D30" s="12" t="inlineStr">
         <is>
           <t>Principes et interface Grasshopper</t>
         </is>
@@ -2972,12 +2972,12 @@
           <t>REF-027</t>
         </is>
       </c>
-      <c r="C31" s="13" t="inlineStr">
+      <c r="C31" s="12" t="inlineStr">
         <is>
           <t>2 – Environnement et principes Grasshopper</t>
         </is>
       </c>
-      <c r="D31" s="13" t="inlineStr">
+      <c r="D31" s="12" t="inlineStr">
         <is>
           <t>Principes et interface Grasshopper</t>
         </is>
@@ -3037,12 +3037,12 @@
           <t>REF-028</t>
         </is>
       </c>
-      <c r="C32" s="13" t="inlineStr">
+      <c r="C32" s="12" t="inlineStr">
         <is>
           <t>2 – Environnement et principes Grasshopper</t>
         </is>
       </c>
-      <c r="D32" s="13" t="inlineStr">
+      <c r="D32" s="12" t="inlineStr">
         <is>
           <t>Principes et interface Grasshopper</t>
         </is>
@@ -3102,12 +3102,12 @@
           <t>REF-029</t>
         </is>
       </c>
-      <c r="C33" s="13" t="inlineStr">
+      <c r="C33" s="12" t="inlineStr">
         <is>
           <t>2 – Environnement et principes Grasshopper</t>
         </is>
       </c>
-      <c r="D33" s="13" t="inlineStr">
+      <c r="D33" s="12" t="inlineStr">
         <is>
           <t>Écosystème de plugins</t>
         </is>
@@ -3154,7 +3154,7 @@
       </c>
       <c r="Q33" s="10" t="inlineStr">
         <is>
-          <t>PL-02, PL-05, PL-10</t>
+          <t>PL-02, PL-05, PL-10, PL-13, PL-16</t>
         </is>
       </c>
     </row>
@@ -3167,12 +3167,12 @@
           <t>REF-030</t>
         </is>
       </c>
-      <c r="C34" s="13" t="inlineStr">
+      <c r="C34" s="12" t="inlineStr">
         <is>
           <t>2 – Environnement et principes Grasshopper</t>
         </is>
       </c>
-      <c r="D34" s="13" t="inlineStr">
+      <c r="D34" s="12" t="inlineStr">
         <is>
           <t>Écosystème de plugins</t>
         </is>
@@ -3219,7 +3219,7 @@
       </c>
       <c r="Q34" s="10" t="inlineStr">
         <is>
-          <t>PL-02, PL-05, PL-09, PL-10</t>
+          <t>PL-02, PL-05, PL-09, PL-10, PL-13</t>
         </is>
       </c>
     </row>
@@ -3232,12 +3232,12 @@
           <t>REF-031</t>
         </is>
       </c>
-      <c r="C35" s="13" t="inlineStr">
+      <c r="C35" s="12" t="inlineStr">
         <is>
           <t>2 – Environnement et principes Grasshopper</t>
         </is>
       </c>
-      <c r="D35" s="13" t="inlineStr">
+      <c r="D35" s="12" t="inlineStr">
         <is>
           <t>Écosystème de plugins</t>
         </is>
@@ -3284,7 +3284,7 @@
       </c>
       <c r="Q35" s="10" t="inlineStr">
         <is>
-          <t>PL-03, PL-08, PL-11</t>
+          <t>PL-03, PL-08, PL-11, PL-14</t>
         </is>
       </c>
     </row>
@@ -3297,12 +3297,12 @@
           <t>REF-032</t>
         </is>
       </c>
-      <c r="C36" s="13" t="inlineStr">
+      <c r="C36" s="12" t="inlineStr">
         <is>
           <t>2 – Environnement et principes Grasshopper</t>
         </is>
       </c>
-      <c r="D36" s="13" t="inlineStr">
+      <c r="D36" s="12" t="inlineStr">
         <is>
           <t>Écosystème de plugins</t>
         </is>
@@ -3349,7 +3349,7 @@
       </c>
       <c r="Q36" s="10" t="inlineStr">
         <is>
-          <t>PL-03, PL-08</t>
+          <t>PL-03, PL-08, PL-14</t>
         </is>
       </c>
     </row>
@@ -3362,12 +3362,12 @@
           <t>REF-033</t>
         </is>
       </c>
-      <c r="C37" s="13" t="inlineStr">
+      <c r="C37" s="12" t="inlineStr">
         <is>
           <t>2 – Environnement et principes Grasshopper</t>
         </is>
       </c>
-      <c r="D37" s="13" t="inlineStr">
+      <c r="D37" s="12" t="inlineStr">
         <is>
           <t>Écosystème de plugins</t>
         </is>
@@ -3414,7 +3414,7 @@
       </c>
       <c r="Q37" s="10" t="inlineStr">
         <is>
-          <t>PL-03, PL-08</t>
+          <t>PL-03, PL-08, PL-14</t>
         </is>
       </c>
     </row>
@@ -3427,12 +3427,12 @@
           <t>REF-034</t>
         </is>
       </c>
-      <c r="C38" s="13" t="inlineStr">
+      <c r="C38" s="12" t="inlineStr">
         <is>
           <t>2 – Environnement et principes Grasshopper</t>
         </is>
       </c>
-      <c r="D38" s="13" t="inlineStr">
+      <c r="D38" s="12" t="inlineStr">
         <is>
           <t>Écosystème de plugins</t>
         </is>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="Q38" s="10" t="inlineStr">
         <is>
-          <t>PL-03, PL-11</t>
+          <t>PL-03, PL-11, PL-14</t>
         </is>
       </c>
     </row>
@@ -3492,12 +3492,12 @@
           <t>REF-035</t>
         </is>
       </c>
-      <c r="C39" s="13" t="inlineStr">
+      <c r="C39" s="12" t="inlineStr">
         <is>
           <t>2 – Environnement et principes Grasshopper</t>
         </is>
       </c>
-      <c r="D39" s="13" t="inlineStr">
+      <c r="D39" s="12" t="inlineStr">
         <is>
           <t>Écosystème de plugins</t>
         </is>
@@ -3544,7 +3544,7 @@
       </c>
       <c r="Q39" s="10" t="inlineStr">
         <is>
-          <t>PL-03, PL-11</t>
+          <t>PL-03, PL-11, PL-14</t>
         </is>
       </c>
     </row>
@@ -3557,12 +3557,12 @@
           <t>REF-036</t>
         </is>
       </c>
-      <c r="C40" s="13" t="inlineStr">
+      <c r="C40" s="12" t="inlineStr">
         <is>
           <t>2 – Environnement et principes Grasshopper</t>
         </is>
       </c>
-      <c r="D40" s="13" t="inlineStr">
+      <c r="D40" s="12" t="inlineStr">
         <is>
           <t>Écosystème de plugins</t>
         </is>
@@ -3609,7 +3609,7 @@
       </c>
       <c r="Q40" s="10" t="inlineStr">
         <is>
-          <t>PL-03, PL-11</t>
+          <t>PL-03, PL-11, PL-14</t>
         </is>
       </c>
     </row>
@@ -3622,12 +3622,12 @@
           <t>REF-037</t>
         </is>
       </c>
-      <c r="C41" s="13" t="inlineStr">
+      <c r="C41" s="12" t="inlineStr">
         <is>
           <t>2 – Environnement et principes Grasshopper</t>
         </is>
       </c>
-      <c r="D41" s="13" t="inlineStr">
+      <c r="D41" s="12" t="inlineStr">
         <is>
           <t>Écosystème de plugins</t>
         </is>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="Q41" s="10" t="inlineStr">
         <is>
-          <t>PL-03, PL-11</t>
+          <t>PL-03, PL-11, PL-14</t>
         </is>
       </c>
     </row>
@@ -3687,12 +3687,12 @@
           <t>REF-038</t>
         </is>
       </c>
-      <c r="C42" s="13" t="inlineStr">
+      <c r="C42" s="12" t="inlineStr">
         <is>
           <t>2 – Environnement et principes Grasshopper</t>
         </is>
       </c>
-      <c r="D42" s="13" t="inlineStr">
+      <c r="D42" s="12" t="inlineStr">
         <is>
           <t>Écosystème de plugins</t>
         </is>
@@ -3739,7 +3739,7 @@
       </c>
       <c r="Q42" s="10" t="inlineStr">
         <is>
-          <t>PL-04, PL-06, PL-07</t>
+          <t>PL-04, PL-06, PL-07, PL-15, PL-16</t>
         </is>
       </c>
     </row>
@@ -3752,12 +3752,12 @@
           <t>REF-039</t>
         </is>
       </c>
-      <c r="C43" s="13" t="inlineStr">
+      <c r="C43" s="12" t="inlineStr">
         <is>
           <t>2 – Environnement et principes Grasshopper</t>
         </is>
       </c>
-      <c r="D43" s="13" t="inlineStr">
+      <c r="D43" s="12" t="inlineStr">
         <is>
           <t>Écosystème de plugins</t>
         </is>
@@ -3804,7 +3804,7 @@
       </c>
       <c r="Q43" s="10" t="inlineStr">
         <is>
-          <t>PL-04, PL-06, PL-07, PL-12</t>
+          <t>PL-04, PL-06, PL-07, PL-12, PL-15, PL-16</t>
         </is>
       </c>
     </row>
@@ -6278,7 +6278,7 @@
       </c>
       <c r="Q81" s="10" t="inlineStr">
         <is>
-          <t>GP-02</t>
+          <t>GP-02, GP-13</t>
         </is>
       </c>
     </row>
@@ -6336,14 +6336,14 @@
       <c r="M82" s="7" t="inlineStr"/>
       <c r="N82" s="8" t="inlineStr"/>
       <c r="O82" s="10" t="inlineStr"/>
-      <c r="P82" s="12" t="inlineStr">
-        <is>
-          <t>Connaissance</t>
+      <c r="P82" s="11" t="inlineStr">
+        <is>
+          <t>Compétence</t>
         </is>
       </c>
       <c r="Q82" s="10" t="inlineStr">
         <is>
-          <t>GP-10</t>
+          <t>GP-10, GP-13</t>
         </is>
       </c>
     </row>
@@ -6408,7 +6408,7 @@
       </c>
       <c r="Q83" s="10" t="inlineStr">
         <is>
-          <t>GP-11</t>
+          <t>GP-11, GP-13</t>
         </is>
       </c>
     </row>
@@ -7636,7 +7636,7 @@
       <c r="M102" s="7" t="inlineStr"/>
       <c r="N102" s="8" t="inlineStr"/>
       <c r="O102" s="10" t="inlineStr"/>
-      <c r="P102" s="12" t="inlineStr">
+      <c r="P102" s="13" t="inlineStr">
         <is>
           <t>Connaissance</t>
         </is>
@@ -7701,7 +7701,7 @@
       <c r="M103" s="7" t="inlineStr"/>
       <c r="N103" s="8" t="inlineStr"/>
       <c r="O103" s="10" t="inlineStr"/>
-      <c r="P103" s="12" t="inlineStr">
+      <c r="P103" s="13" t="inlineStr">
         <is>
           <t>Connaissance</t>
         </is>
@@ -8091,7 +8091,7 @@
       <c r="M109" s="7" t="inlineStr"/>
       <c r="N109" s="8" t="inlineStr"/>
       <c r="O109" s="10" t="inlineStr"/>
-      <c r="P109" s="12" t="inlineStr">
+      <c r="P109" s="13" t="inlineStr">
         <is>
           <t>Connaissance</t>
         </is>
@@ -8221,7 +8221,7 @@
       <c r="M111" s="7" t="inlineStr"/>
       <c r="N111" s="8" t="inlineStr"/>
       <c r="O111" s="10" t="inlineStr"/>
-      <c r="P111" s="12" t="inlineStr">
+      <c r="P111" s="13" t="inlineStr">
         <is>
           <t>Connaissance</t>
         </is>
@@ -8871,7 +8871,7 @@
       <c r="M121" s="7" t="inlineStr"/>
       <c r="N121" s="8" t="inlineStr"/>
       <c r="O121" s="10" t="inlineStr"/>
-      <c r="P121" s="12" t="inlineStr">
+      <c r="P121" s="13" t="inlineStr">
         <is>
           <t>Connaissance</t>
         </is>
@@ -9203,7 +9203,7 @@
       </c>
       <c r="Q126" s="10" t="inlineStr">
         <is>
-          <t>WB-02</t>
+          <t>WB-02, WB-11</t>
         </is>
       </c>
     </row>
@@ -9268,7 +9268,7 @@
       </c>
       <c r="Q127" s="10" t="inlineStr">
         <is>
-          <t>WB-02, WB-06</t>
+          <t>WB-02, WB-06, WB-11</t>
         </is>
       </c>
     </row>
@@ -9333,7 +9333,7 @@
       </c>
       <c r="Q128" s="10" t="inlineStr">
         <is>
-          <t>WB-02, WB-07</t>
+          <t>WB-02, WB-07, WB-11</t>
         </is>
       </c>
     </row>
@@ -9391,14 +9391,14 @@
       <c r="M129" s="7" t="inlineStr"/>
       <c r="N129" s="8" t="inlineStr"/>
       <c r="O129" s="10" t="inlineStr"/>
-      <c r="P129" s="12" t="inlineStr">
-        <is>
-          <t>Connaissance</t>
+      <c r="P129" s="11" t="inlineStr">
+        <is>
+          <t>Compétence</t>
         </is>
       </c>
       <c r="Q129" s="10" t="inlineStr">
         <is>
-          <t>WB-03</t>
+          <t>WB-03, WB-10</t>
         </is>
       </c>
     </row>
@@ -9463,7 +9463,7 @@
       </c>
       <c r="Q130" s="10" t="inlineStr">
         <is>
-          <t>WB-03, WB-05</t>
+          <t>WB-03, WB-05, WB-10</t>
         </is>
       </c>
     </row>
@@ -9528,7 +9528,7 @@
       </c>
       <c r="Q131" s="10" t="inlineStr">
         <is>
-          <t>WB-09</t>
+          <t>WB-09, WB-10</t>
         </is>
       </c>
     </row>
@@ -9911,7 +9911,7 @@
       <c r="M137" s="7" t="inlineStr"/>
       <c r="N137" s="8" t="inlineStr"/>
       <c r="O137" s="10" t="inlineStr"/>
-      <c r="P137" s="12" t="inlineStr">
+      <c r="P137" s="13" t="inlineStr">
         <is>
           <t>Connaissance</t>
         </is>
@@ -9983,7 +9983,7 @@
       </c>
       <c r="Q138" s="10" t="inlineStr">
         <is>
-          <t>IA-01</t>
+          <t>IA-01, IA-32</t>
         </is>
       </c>
     </row>
@@ -10041,7 +10041,7 @@
       <c r="M139" s="7" t="inlineStr"/>
       <c r="N139" s="8" t="inlineStr"/>
       <c r="O139" s="10" t="inlineStr"/>
-      <c r="P139" s="12" t="inlineStr">
+      <c r="P139" s="13" t="inlineStr">
         <is>
           <t>Connaissance</t>
         </is>
@@ -10113,7 +10113,7 @@
       </c>
       <c r="Q140" s="10" t="inlineStr">
         <is>
-          <t>IA-03</t>
+          <t>IA-03, IA-32</t>
         </is>
       </c>
     </row>
@@ -10308,7 +10308,7 @@
       </c>
       <c r="Q143" s="10" t="inlineStr">
         <is>
-          <t>IA-06</t>
+          <t>IA-06, IA-26</t>
         </is>
       </c>
     </row>
@@ -10373,7 +10373,7 @@
       </c>
       <c r="Q144" s="10" t="inlineStr">
         <is>
-          <t>IA-06, IA-22</t>
+          <t>IA-06, IA-22, IA-26</t>
         </is>
       </c>
     </row>
@@ -10438,7 +10438,7 @@
       </c>
       <c r="Q145" s="10" t="inlineStr">
         <is>
-          <t>IA-05</t>
+          <t>IA-05, IA-27</t>
         </is>
       </c>
     </row>
@@ -10691,14 +10691,14 @@
       <c r="M149" s="7" t="inlineStr"/>
       <c r="N149" s="8" t="inlineStr"/>
       <c r="O149" s="10" t="inlineStr"/>
-      <c r="P149" s="12" t="inlineStr">
-        <is>
-          <t>Connaissance</t>
+      <c r="P149" s="11" t="inlineStr">
+        <is>
+          <t>Compétence</t>
         </is>
       </c>
       <c r="Q149" s="10" t="inlineStr">
         <is>
-          <t>IA-08</t>
+          <t>IA-08, IA-29</t>
         </is>
       </c>
     </row>
@@ -10828,7 +10828,7 @@
       </c>
       <c r="Q151" s="10" t="inlineStr">
         <is>
-          <t>IA-10, IA-19</t>
+          <t>IA-10, IA-19, IA-28</t>
         </is>
       </c>
     </row>
@@ -11088,7 +11088,7 @@
       </c>
       <c r="Q155" s="10" t="inlineStr">
         <is>
-          <t>IA-11, IA-17</t>
+          <t>IA-11, IA-17, IA-33</t>
         </is>
       </c>
     </row>
@@ -11218,7 +11218,7 @@
       </c>
       <c r="Q157" s="10" t="inlineStr">
         <is>
-          <t>IA-12</t>
+          <t>IA-12, IA-31</t>
         </is>
       </c>
     </row>
@@ -11283,7 +11283,7 @@
       </c>
       <c r="Q158" s="10" t="inlineStr">
         <is>
-          <t>IA-12, IA-15</t>
+          <t>IA-12, IA-15, IA-31</t>
         </is>
       </c>
     </row>
@@ -11348,7 +11348,7 @@
       </c>
       <c r="Q159" s="10" t="inlineStr">
         <is>
-          <t>IA-12, IA-16</t>
+          <t>IA-12, IA-16, IA-31</t>
         </is>
       </c>
     </row>
@@ -11471,7 +11471,7 @@
       <c r="M161" s="7" t="inlineStr"/>
       <c r="N161" s="8" t="inlineStr"/>
       <c r="O161" s="10" t="inlineStr"/>
-      <c r="P161" s="12" t="inlineStr">
+      <c r="P161" s="13" t="inlineStr">
         <is>
           <t>Connaissance</t>
         </is>
@@ -11536,7 +11536,7 @@
       <c r="M162" s="7" t="inlineStr"/>
       <c r="N162" s="8" t="inlineStr"/>
       <c r="O162" s="10" t="inlineStr"/>
-      <c r="P162" s="12" t="inlineStr">
+      <c r="P162" s="13" t="inlineStr">
         <is>
           <t>Connaissance</t>
         </is>
@@ -11608,7 +11608,7 @@
       </c>
       <c r="Q163" s="10" t="inlineStr">
         <is>
-          <t>IA-14, IA-25</t>
+          <t>IA-14, IA-25, IA-30</t>
         </is>
       </c>
     </row>
